--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45488</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>45217</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>44902</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45798</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>44433</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45161</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>44103</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44616</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45672</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45152</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44820</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44132</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44412</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45624</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44980</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44749</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44433</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45589</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44501</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45618</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45558.44512731482</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45300</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45590</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44601</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44501</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>45103</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>45695</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45560.43387731481</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44902</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>45411</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45363</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45572.42619212963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45016</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44615</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44494</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44616</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>44795</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44795</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45463</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45595</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45299</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44543</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45470</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45791.57008101852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45595</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45594</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45622</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44897</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45798</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45231</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45251</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45602</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45579</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44376</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44081</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44147</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44386</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44403</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44495</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>44426</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44095</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44585</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44120</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44469</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44403</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44874</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>44354</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44711</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44475</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44784</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44120</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44407</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44405</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44109</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44105</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44067</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44490</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44839</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44777</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44761</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44805</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44564</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44439</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44742</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44711</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>44805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44515</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44109</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>44201</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>44183</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>44459</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44846</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>44481</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>44123</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44704</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>44551</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44726</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44544</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44454</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44496</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44358</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44513</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44558</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>44760</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>44484</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>44484</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>44749</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>44277</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>44123</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44809</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44102</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44837</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44429</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44182</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44433</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44469</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>44875</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44062</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>44509</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44277</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44095</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44673</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44531</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>44439</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>44120</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44282</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>44537</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44545</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>44182</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44182</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44670</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44846</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45091</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45070.66266203704</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44826</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>44924</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45107</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45328</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44083</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45554</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44820</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45063</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>44788</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45709</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>44620</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45751</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44642</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45594</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45593</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45378</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45155</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45635</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45308</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45583</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45091</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>44823</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45211</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45135</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45103</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44876</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44477</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45101</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45373</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45233</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45219</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45701</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44901</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>44466</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45406</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45393</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45732</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>44909</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45378</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>44158</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45555</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>44903</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45615</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44980</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27234,7 +27234,7 @@
         <v>45595</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44886</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45364</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>45588</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>44896</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45271</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45101</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>44903</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45408</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45174</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45155</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45279</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44910</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45442</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45320</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>45373</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45226</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44909</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>44909</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44909</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>45140</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45546</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45035</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45428</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45603</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44901</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45561</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45393</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45281</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45363</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>45079</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44091</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44908</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44851</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44943</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>44120</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45779</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45307</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45618</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>44550</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44637</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45021</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45560.34564814815</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45281</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44911</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45783.45171296296</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45280</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44915</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45545</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45040</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45014</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>45786.49009259259</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44924</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45786</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45611.49162037037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>44412</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45786.53510416667</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45245</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45705</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>44496</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45182</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45145</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45320</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38582,7 +38582,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45790.61496527777</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45454</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45544</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45789</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44581</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45117</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>44383</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45560.34431712963</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45791.56130787037</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>44952</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45576</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45663</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45791.5678587963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>45791.56569444444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45604</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45415</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45371</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44910</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45796</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44440</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44735</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45772</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>44566</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45457</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45147</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45142</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45453</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45603</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45205</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45601</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>45798</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>45798</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>44641</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45006.49</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45663</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45226</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>45093</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45313</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>44981</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>44698</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45716</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>44735</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45281</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>44571</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45694</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44491</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45799.61583333334</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>44789</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45075</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45075</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47587,7 +47587,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45117</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44933</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>45107</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>45226</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45740</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>44994</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49211,7 +49211,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45687</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45805</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45805</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>44952</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50168,7 +50168,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45261</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45621.595</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45457</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>45457</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45757.4546875</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44719</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45316</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>44900</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51621,7 +51621,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51802,7 +51802,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45103</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51988,7 +51988,7 @@
         <v>45103</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45142</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45616</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52298,7 +52298,7 @@
         <v>45251</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52484,7 +52484,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52541,7 +52541,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45672</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52955,7 +52955,7 @@
         <v>45713.36498842593</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45223</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45271</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>44733</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>45681</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53617,7 +53617,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53679,7 +53679,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53741,7 +53741,7 @@
         <v>45124</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53803,7 +53803,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53860,7 +53860,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54046,7 +54046,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>44830</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54165,7 +54165,7 @@
         <v>45135</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45849</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54408,7 +54408,7 @@
         <v>45279</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>44900</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45713.54880787037</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45849</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54884,7 +54884,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55132,7 +55132,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55194,7 +55194,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>45154</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>45735.42790509259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55437,7 +55437,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45735.4485300926</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>44735</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>45701</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45239</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56089,7 +56089,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45149</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>45713</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56384,7 +56384,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56508,7 +56508,7 @@
         <v>44887</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45279</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45815</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56860,7 +56860,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>45488</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56984,7 +56984,7 @@
         <v>44761</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57041,7 +57041,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45691</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57403,7 +57403,7 @@
         <v>45530</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45530</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45247</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58008,7 +58008,7 @@
         <v>45819</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58070,7 +58070,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>45820</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58318,7 +58318,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58380,7 +58380,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58504,7 +58504,7 @@
         <v>45239</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>44522</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58990,7 +58990,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59052,7 +59052,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59176,7 +59176,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59238,7 +59238,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59300,7 +59300,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>44062</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59471,7 +59471,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59528,7 +59528,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59585,7 +59585,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59647,7 +59647,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59818,7 +59818,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59875,7 +59875,7 @@
         <v>44812</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59994,7 +59994,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60113,7 +60113,7 @@
         <v>45223</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60175,7 +60175,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60418,7 +60418,7 @@
         <v>45666</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60537,7 +60537,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60661,7 +60661,7 @@
         <v>44403</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60775,7 +60775,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>44820</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>45813</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61137,7 +61137,7 @@
         <v>44907</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61194,7 +61194,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61256,7 +61256,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61318,7 +61318,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61380,7 +61380,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>44826</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>45176</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61737,7 +61737,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61799,7 +61799,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61923,7 +61923,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61980,7 +61980,7 @@
         <v>45279</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62037,7 +62037,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>44874</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62275,7 +62275,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62337,7 +62337,7 @@
         <v>45775</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62394,7 +62394,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62451,7 +62451,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62513,7 +62513,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62570,7 +62570,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62632,7 +62632,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62694,7 +62694,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62756,7 +62756,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62937,7 +62937,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63180,7 +63180,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>44620</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63361,7 +63361,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63418,7 +63418,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63542,7 +63542,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63604,7 +63604,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63728,7 +63728,7 @@
         <v>44894</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63852,7 +63852,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63914,7 +63914,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64038,7 +64038,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64162,7 +64162,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64224,7 +64224,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64286,7 +64286,7 @@
         <v>44861</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>45468</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64405,7 +64405,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64581,7 +64581,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64705,7 +64705,7 @@
         <v>45740</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64767,7 +64767,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64829,7 +64829,7 @@
         <v>44875</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64891,7 +64891,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64953,7 +64953,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65015,7 +65015,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65077,7 +65077,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65139,7 +65139,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65201,7 +65201,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65263,7 +65263,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65325,7 +65325,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65444,7 +65444,7 @@
         <v>44847</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65501,7 +65501,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65563,7 +65563,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65625,7 +65625,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65682,7 +65682,7 @@
         <v>44501</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65744,7 +65744,7 @@
         <v>44830</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65801,7 +65801,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65858,7 +65858,7 @@
         <v>44603</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65915,7 +65915,7 @@
         <v>44424</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65977,7 +65977,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66034,7 +66034,7 @@
         <v>44874</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66091,7 +66091,7 @@
         <v>44890</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>45561</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66334,7 +66334,7 @@
         <v>45107</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66391,7 +66391,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
         <v>45266</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>44323</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>44826</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>44369</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66681,7 +66681,7 @@
         <v>44580</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66738,7 +66738,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66800,7 +66800,7 @@
         <v>44881</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66857,7 +66857,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67095,7 +67095,7 @@
         <v>45015</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67152,7 +67152,7 @@
         <v>45223</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67209,7 +67209,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>45058</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         <v>45020</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67385,7 +67385,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67442,7 +67442,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67499,7 +67499,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67561,7 +67561,7 @@
         <v>44952</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -67623,7 +67623,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -67685,7 +67685,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67742,7 +67742,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67804,7 +67804,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67866,7 +67866,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67928,7 +67928,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67985,7 +67985,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68047,7 +68047,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68109,7 +68109,7 @@
         <v>44603</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68166,7 +68166,7 @@
         <v>45097</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68228,7 +68228,7 @@
         <v>45238</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68285,7 +68285,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68347,7 +68347,7 @@
         <v>45041</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68409,7 +68409,7 @@
         <v>45462</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68466,7 +68466,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68523,7 +68523,7 @@
         <v>45156</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -68585,7 +68585,7 @@
         <v>45599</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -68647,7 +68647,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -68709,7 +68709,7 @@
         <v>45541</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68771,7 +68771,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68833,7 +68833,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68890,7 +68890,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68947,7 +68947,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69009,7 +69009,7 @@
         <v>45176</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69066,7 +69066,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69190,7 +69190,7 @@
         <v>44529</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>45503</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45488</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>45217</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>44902</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45798</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>44433</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45161</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>44103</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44616</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45672</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45152</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44820</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44132</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44412</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45624</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44980</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44749</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44433</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45589</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44501</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45618</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45558.44512731482</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45300</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45590</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44601</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44501</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>45103</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>45695</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45560.43387731481</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44902</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>45411</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45363</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45572.42619212963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45016</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44615</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44494</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44616</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>44795</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44795</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45463</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45595</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45299</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44543</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45470</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45791.57008101852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45595</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45594</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45622</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44897</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45798</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45231</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45251</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45602</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45579</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44376</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44081</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44147</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44386</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44403</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44495</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>44426</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44095</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44585</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44120</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44469</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44403</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44874</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>44354</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44711</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44475</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44784</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44120</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44407</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44405</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44109</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44105</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44067</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44490</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44839</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44777</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44761</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44805</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44564</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44439</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44742</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44711</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>44805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44515</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44109</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>44201</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>44183</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>44459</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44846</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>44481</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>44123</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44704</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>44551</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44726</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44544</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44454</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44496</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44358</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44513</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44558</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>44760</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>44484</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>44484</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>44749</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>44277</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>44123</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44809</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44102</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44837</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44429</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44182</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44433</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44469</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>44875</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44062</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>44509</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44277</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44095</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44673</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44531</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>44439</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>44120</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44282</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>44537</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44545</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>44182</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44182</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44670</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44846</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45091</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45070.66266203704</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44826</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>44924</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45107</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45328</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44083</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45554</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44820</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45063</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>44788</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45709</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>44620</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45751</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44642</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45594</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45593</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45098</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45378</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45155</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45635</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45308</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45583</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45091</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>44823</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45211</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45135</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45103</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44876</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44477</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45101</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45373</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45233</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45219</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45701</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44901</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>44466</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45406</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45393</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45732</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>44909</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45378</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>44158</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45555</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>44903</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45615</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44980</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27234,7 +27234,7 @@
         <v>45595</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44886</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45364</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>45588</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>44896</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45271</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45101</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>44903</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45469</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45408</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45174</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45155</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45279</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44910</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45442</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45320</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>45373</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45226</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>44909</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>44909</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44909</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>45140</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45546</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45035</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45428</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45603</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45600</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44901</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45561</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45393</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45281</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45363</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>45079</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44091</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44908</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44851</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44943</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>44120</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45779</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45307</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45618</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>44550</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44637</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45021</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45560.34564814815</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45281</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44911</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45783.45171296296</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45280</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44915</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45545</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45040</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45014</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>45786.49009259259</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44924</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45786</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45611.49162037037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>44412</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45786.53510416667</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45245</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45705</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>44496</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45182</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45145</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45320</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38582,7 +38582,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45790.61496527777</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45454</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45544</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45789</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44581</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45117</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>44383</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45560.34431712963</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45791.56130787037</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>44952</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45576</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45663</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45791.5678587963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>45791.56569444444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45604</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45415</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45371</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44910</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45796</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44440</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44735</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45772</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>44566</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45457</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45147</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45142</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45453</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45603</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45205</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45601</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>45798</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>45798</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>44641</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45006.49</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45663</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45226</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>45093</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45313</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>44981</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>44698</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45716</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>44735</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45281</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>44571</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45694</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44491</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45799.61583333334</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>44789</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45075</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45075</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47587,7 +47587,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45117</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44933</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>45107</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>45226</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45740</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>44994</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49211,7 +49211,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45687</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45805</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45805</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>44952</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50168,7 +50168,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45261</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45621.595</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45457</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>45457</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45757.4546875</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>44719</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45316</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>44900</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51621,7 +51621,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51802,7 +51802,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45103</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51988,7 +51988,7 @@
         <v>45103</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45142</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45616</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52298,7 +52298,7 @@
         <v>45251</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52484,7 +52484,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52541,7 +52541,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45672</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52955,7 +52955,7 @@
         <v>45713.36498842593</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45223</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45271</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>44733</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>45681</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53617,7 +53617,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53679,7 +53679,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53741,7 +53741,7 @@
         <v>45124</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53803,7 +53803,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53860,7 +53860,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54046,7 +54046,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>44830</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54165,7 +54165,7 @@
         <v>45135</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45849</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54408,7 +54408,7 @@
         <v>45279</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>44900</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45713.54880787037</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45849</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54884,7 +54884,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55132,7 +55132,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55194,7 +55194,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>45154</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>45735.42790509259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55437,7 +55437,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45735.4485300926</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>44735</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>45701</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45239</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56089,7 +56089,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45149</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>45713</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56384,7 +56384,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56508,7 +56508,7 @@
         <v>44887</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45279</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45815</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56860,7 +56860,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>45488</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56984,7 +56984,7 @@
         <v>44761</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57041,7 +57041,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45691</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57403,7 +57403,7 @@
         <v>45530</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45530</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45247</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58008,7 +58008,7 @@
         <v>45819</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58070,7 +58070,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>45820</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58318,7 +58318,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58380,7 +58380,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58504,7 +58504,7 @@
         <v>45239</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>44522</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58990,7 +58990,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59052,7 +59052,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59176,7 +59176,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59238,7 +59238,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59300,7 +59300,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>44062</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59471,7 +59471,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59528,7 +59528,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59585,7 +59585,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59647,7 +59647,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59818,7 +59818,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59875,7 +59875,7 @@
         <v>44812</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59994,7 +59994,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60113,7 +60113,7 @@
         <v>45223</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60175,7 +60175,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60418,7 +60418,7 @@
         <v>45666</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60537,7 +60537,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60661,7 +60661,7 @@
         <v>44403</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60775,7 +60775,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>44820</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>45813</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61137,7 +61137,7 @@
         <v>44907</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61194,7 +61194,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61256,7 +61256,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61318,7 +61318,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61380,7 +61380,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>44826</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>45176</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61737,7 +61737,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61799,7 +61799,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61923,7 +61923,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61980,7 +61980,7 @@
         <v>45279</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62037,7 +62037,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>44874</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62275,7 +62275,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62337,7 +62337,7 @@
         <v>45775</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62394,7 +62394,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62451,7 +62451,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62513,7 +62513,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62570,7 +62570,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62632,7 +62632,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62694,7 +62694,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62756,7 +62756,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62937,7 +62937,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63180,7 +63180,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>44620</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63361,7 +63361,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63418,7 +63418,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63542,7 +63542,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63604,7 +63604,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63728,7 +63728,7 @@
         <v>44894</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63852,7 +63852,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63914,7 +63914,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64038,7 +64038,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64162,7 +64162,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64224,7 +64224,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64286,7 +64286,7 @@
         <v>44861</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>45468</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64405,7 +64405,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64581,7 +64581,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64705,7 +64705,7 @@
         <v>45740</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64767,7 +64767,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64829,7 +64829,7 @@
         <v>44875</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64891,7 +64891,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64953,7 +64953,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65015,7 +65015,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65077,7 +65077,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65139,7 +65139,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65201,7 +65201,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65263,7 +65263,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65325,7 +65325,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65444,7 +65444,7 @@
         <v>44847</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65501,7 +65501,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65563,7 +65563,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65625,7 +65625,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65682,7 +65682,7 @@
         <v>44501</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65744,7 +65744,7 @@
         <v>44830</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65801,7 +65801,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65858,7 +65858,7 @@
         <v>44603</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65915,7 +65915,7 @@
         <v>44424</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65977,7 +65977,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66034,7 +66034,7 @@
         <v>44874</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66091,7 +66091,7 @@
         <v>44890</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>45561</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66334,7 +66334,7 @@
         <v>45107</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66391,7 +66391,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
         <v>45266</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>44323</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>44826</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>44369</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66681,7 +66681,7 @@
         <v>44580</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66738,7 +66738,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66800,7 +66800,7 @@
         <v>44881</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66857,7 +66857,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67095,7 +67095,7 @@
         <v>45015</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67152,7 +67152,7 @@
         <v>45223</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67209,7 +67209,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>45058</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         <v>45020</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67385,7 +67385,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67442,7 +67442,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67499,7 +67499,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67561,7 +67561,7 @@
         <v>44952</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -67623,7 +67623,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -67685,7 +67685,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67742,7 +67742,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67804,7 +67804,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67866,7 +67866,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67928,7 +67928,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67985,7 +67985,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68047,7 +68047,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68109,7 +68109,7 @@
         <v>44603</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68166,7 +68166,7 @@
         <v>45097</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68228,7 +68228,7 @@
         <v>45238</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68285,7 +68285,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68347,7 +68347,7 @@
         <v>45041</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68409,7 +68409,7 @@
         <v>45462</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68466,7 +68466,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68523,7 +68523,7 @@
         <v>45156</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -68585,7 +68585,7 @@
         <v>45599</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -68647,7 +68647,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -68709,7 +68709,7 @@
         <v>45541</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68771,7 +68771,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68833,7 +68833,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68890,7 +68890,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68947,7 +68947,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69009,7 +69009,7 @@
         <v>45176</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69066,7 +69066,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69190,7 +69190,7 @@
         <v>44529</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>45503</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45488</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44433</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44902</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45877.46135416667</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45217</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45798</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44103</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45161</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44616</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45672</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45152</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44820</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44132</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44412</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44980</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>45624</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44749</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44433</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45589</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44501</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45231</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45300</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45590</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45618</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>45558.44512731482</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>44601</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44501</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45103</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45411</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44902</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>45877.56935185185</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45572.42619212963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45363</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45016</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45695</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45560.43387731481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44615</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44494</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44616</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44795</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44795</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45299</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44543</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45791.57008101852</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45470</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45798</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45622</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45463</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45231</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>45251</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45881.41111111111</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45595</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45602</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45594</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44897</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45579</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>44376</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44081</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44147</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44386</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>44403</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44426</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44095</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44585</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44120</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44148</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44469</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44403</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44874</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>44354</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44711</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44784</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44120</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>44407</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44405</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>44109</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>44105</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>44067</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44490</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44839</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44777</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>44761</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44805</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44564</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44439</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44742</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>44711</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>44805</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44515</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44109</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44201</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44183</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44459</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44481</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44123</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44551</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44496</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44358</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44760</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>44513</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44558</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44484</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44484</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44749</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44277</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44123</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44809</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44837</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44102</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44429</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>44182</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>44433</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>44469</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>44875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44509</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>44062</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44277</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44673</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>44095</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44531</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>44439</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44282</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44120</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>44545</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>44537</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44182</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44182</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44846</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>44704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>44726</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>44846</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45378</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>44454</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>44544</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>44826</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45135</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45554</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>44820</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>44788</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45373</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45455</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45600</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>44901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45363</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45079</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44901</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45393</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44909</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45378</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45281</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44091</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44908</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44120</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45779</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>44158</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>44880</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45021</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45560.34564814815</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45783.45171296296</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45281</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45280</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45040</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45014</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45786.49009259259</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45786</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44412</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45786.53510416667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45790.61496527777</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45705</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45789</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44496</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>45145</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45791.56130787037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45791.5678587963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45454</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>44581</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45791.56569444444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45560.34431712963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45576</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44910</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45796</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44440</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45457</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45453</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45604</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>45798</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>45798</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45415</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>45799.61583333334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45147</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45603</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>45601</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45805</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45805</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>44896</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45093</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>44903</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45313</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>44698</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45469</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45716</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45621.595</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45408</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45757.4546875</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44910</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45586</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>45442</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45316</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45320</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>44789</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45117</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45226</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>44909</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45140</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45107</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>45226</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>45740</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45245</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45687</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45035</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45223</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>45428</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45603</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45849</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45279</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45561</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45713.54880787037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45849</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45261</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45393</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>44719</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44943</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38665,7 +38665,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>45307</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45618</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44550</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45488</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45251</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>44637</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>45691</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>44911</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>45247</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44915</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>45545</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45819</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45124</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44830</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45135</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>44900</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45735.42790509259</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45735.4485300926</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45239</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44924</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45611.49162037037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45713</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44887</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>45279</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>44761</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45182</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45530</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45530</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44561,7 +44561,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45041</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44923,7 +44923,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45320</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45078</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45239</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>44522</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45544</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45117</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44062</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>44383</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>44952</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45663</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45271</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48444,7 +48444,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48739,7 +48739,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48801,7 +48801,7 @@
         <v>44620</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>44894</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>45813</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45881.63590277778</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45881.6677199074</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>45881.67791666667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45468</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45880</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45740</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>44875</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45881.40667824074</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45371</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>44735</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>44847</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51997,7 +51997,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45772</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>45883.49055555555</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>45883.51207175926</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52540,7 +52540,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45882.30746527778</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45142</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>44501</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>44830</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>44603</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>44424</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45205</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53601,7 +53601,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>44641</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45006.49</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>44874</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>44890</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45226</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -54129,7 +54129,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>44981</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54310,7 +54310,7 @@
         <v>45561</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>44735</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45107</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>45266</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45281</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>44323</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>44826</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54771,7 +54771,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54833,7 +54833,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>44369</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54957,7 +54957,7 @@
         <v>44580</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -55014,7 +55014,7 @@
         <v>45694</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>44491</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -55190,7 +55190,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>44881</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55495,7 +55495,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55557,7 +55557,7 @@
         <v>44933</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55614,7 +55614,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55785,7 +55785,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55847,7 +55847,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -56152,7 +56152,7 @@
         <v>44994</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -56209,7 +56209,7 @@
         <v>44952</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45015</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>45223</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45058</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45020</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45457</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45457</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56809,7 +56809,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -57047,7 +57047,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>44900</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57280,7 +57280,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57337,7 +57337,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>45103</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45103</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57642,7 +57642,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>45142</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57766,7 +57766,7 @@
         <v>45616</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57952,7 +57952,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -58009,7 +58009,7 @@
         <v>44952</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -58128,7 +58128,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -58185,7 +58185,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58242,7 +58242,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58304,7 +58304,7 @@
         <v>45672</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58361,7 +58361,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58418,7 +58418,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45713.36498842593</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>45271</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>44733</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -59023,7 +59023,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -59085,7 +59085,7 @@
         <v>45681</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -59204,7 +59204,7 @@
         <v>44603</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59261,7 +59261,7 @@
         <v>45097</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59323,7 +59323,7 @@
         <v>45238</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59504,7 +59504,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>45041</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>45154</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>44735</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>45701</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59866,7 +59866,7 @@
         <v>45462</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59923,7 +59923,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59980,7 +59980,7 @@
         <v>45156</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>45149</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -60099,7 +60099,7 @@
         <v>45599</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60342,7 +60342,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60404,7 +60404,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45541</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60528,7 +60528,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60590,7 +60590,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60652,7 +60652,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60714,7 +60714,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60828,7 +60828,7 @@
         <v>45187</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60890,7 +60890,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60947,7 +60947,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -61004,7 +61004,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -61066,7 +61066,7 @@
         <v>45176</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>44812</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61309,7 +61309,7 @@
         <v>44529</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>45503</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61542,7 +61542,7 @@
         <v>45666</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61661,7 +61661,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61723,7 +61723,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61785,7 +61785,7 @@
         <v>44403</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61842,7 +61842,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61899,7 +61899,7 @@
         <v>44820</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61956,7 +61956,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -62080,7 +62080,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -62142,7 +62142,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -62204,7 +62204,7 @@
         <v>45091</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62266,7 +62266,7 @@
         <v>44907</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62323,7 +62323,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62385,7 +62385,7 @@
         <v>44924</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62442,7 +62442,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62504,7 +62504,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>44826</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62804,7 +62804,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45176</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62985,7 +62985,7 @@
         <v>45279</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -63166,7 +63166,7 @@
         <v>45063</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>44874</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63285,7 +63285,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>45775</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63404,7 +63404,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>45751</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63523,7 +63523,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63585,7 +63585,7 @@
         <v>45594</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63647,7 +63647,7 @@
         <v>45593</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63709,7 +63709,7 @@
         <v>44670</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63766,7 +63766,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63828,7 +63828,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63947,7 +63947,7 @@
         <v>45155</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45635</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -64066,7 +64066,7 @@
         <v>45308</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -64128,7 +64128,7 @@
         <v>45583</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64185,7 +64185,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         <v>45070.66266203704</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64309,7 +64309,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45107</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64433,7 +64433,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         <v>44083</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64552,7 +64552,7 @@
         <v>45211</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64614,7 +64614,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64738,7 +64738,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64800,7 +64800,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>45709</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64971,7 +64971,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>44620</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -65090,7 +65090,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -65147,7 +65147,7 @@
         <v>45101</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65204,7 +65204,7 @@
         <v>44642</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65261,7 +65261,7 @@
         <v>44963</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65318,7 +65318,7 @@
         <v>45098</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65375,7 +65375,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65494,7 +65494,7 @@
         <v>45233</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>45219</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65613,7 +65613,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65675,7 +65675,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65737,7 +65737,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65851,7 +65851,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65913,7 +65913,7 @@
         <v>45091</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65975,7 +65975,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -66032,7 +66032,7 @@
         <v>44823</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -66094,7 +66094,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -66151,7 +66151,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66213,7 +66213,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66275,7 +66275,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45103</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66389,7 +66389,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66446,7 +66446,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66503,7 +66503,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66565,7 +66565,7 @@
         <v>44876</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>44477</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66684,7 +66684,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66741,7 +66741,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66798,7 +66798,7 @@
         <v>45615</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66860,7 +66860,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66917,7 +66917,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66979,7 +66979,7 @@
         <v>45076</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -67036,7 +67036,7 @@
         <v>44980</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -67093,7 +67093,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -67155,7 +67155,7 @@
         <v>45595</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67217,7 +67217,7 @@
         <v>45701</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67274,7 +67274,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67331,7 +67331,7 @@
         <v>45364</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67388,7 +67388,7 @@
         <v>44466</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67445,7 +67445,7 @@
         <v>45406</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67502,7 +67502,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67564,7 +67564,7 @@
         <v>45588</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67621,7 +67621,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67683,7 +67683,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67745,7 +67745,7 @@
         <v>45732</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -67802,7 +67802,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67921,7 +67921,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67983,7 +67983,7 @@
         <v>45555</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -68040,7 +68040,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -68102,7 +68102,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -68164,7 +68164,7 @@
         <v>45174</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68226,7 +68226,7 @@
         <v>44903</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68288,7 +68288,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68345,7 +68345,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68407,7 +68407,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68464,7 +68464,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68588,7 +68588,7 @@
         <v>45155</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68650,7 +68650,7 @@
         <v>45279</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68707,7 +68707,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -68769,7 +68769,7 @@
         <v>45373</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -68826,7 +68826,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -68888,7 +68888,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>44886</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -69069,7 +69069,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -69126,7 +69126,7 @@
         <v>45271</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69183,7 +69183,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69245,7 +69245,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69307,7 +69307,7 @@
         <v>45101</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69364,7 +69364,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69426,7 +69426,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -69483,7 +69483,7 @@
         <v>44909</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -69545,7 +69545,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -69607,7 +69607,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -69669,7 +69669,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -69731,7 +69731,7 @@
         <v>45546</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -69788,7 +69788,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -69845,7 +69845,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -69907,7 +69907,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -69969,7 +69969,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -70031,7 +70031,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45488</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44433</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44902</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45877.46135416667</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45217</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45798</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44103</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45161</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44616</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45672</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45152</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44820</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44132</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44412</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44980</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>45624</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44749</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44433</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45589</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44501</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45231</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45300</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45590</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45618</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>45558.44512731482</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>44601</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44501</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45103</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45411</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44902</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>45877.56935185185</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45572.42619212963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45363</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45016</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45695</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45560.43387731481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44615</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44494</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44616</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44795</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44795</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45299</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44543</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45791.57008101852</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45470</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45798</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45622</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45463</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45231</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>45251</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45881.41111111111</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45595</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45602</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45594</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44897</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45579</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>44376</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44081</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44147</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44386</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>44403</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44426</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44095</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44585</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44120</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44148</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44469</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44403</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44874</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>44354</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44711</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44475</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44784</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44120</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>44407</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44405</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>44109</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>44105</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>44067</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44490</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44839</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44777</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>44761</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44805</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44564</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44439</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44742</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>44711</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>44805</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44515</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44109</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44201</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44183</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44459</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44481</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44123</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44551</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44496</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44358</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44760</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>44513</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44558</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44484</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44484</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44749</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44277</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44123</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44809</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44837</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44102</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44429</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>44182</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>44433</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>44469</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>44875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44509</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>44062</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44277</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44673</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>44095</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44531</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>44439</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44282</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44120</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>44545</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>44537</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44182</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44182</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44846</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>44704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>44726</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>44846</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45378</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>44454</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>44544</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>44826</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45135</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45554</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>44820</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>44788</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45373</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45455</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45600</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>44901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45363</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45079</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44901</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45393</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44909</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45378</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45281</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44091</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44908</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44120</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45779</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>44158</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>44880</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45021</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45560.34564814815</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45783.45171296296</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45281</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45280</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45040</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45014</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45786.49009259259</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45786</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44412</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45786.53510416667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45790.61496527777</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45705</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45789</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44496</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>45145</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45791.56130787037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45791.5678587963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45454</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>44581</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45791.56569444444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45560.34431712963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45576</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44910</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45796</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44440</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45457</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45453</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45604</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>45798</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>45798</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45415</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>45799.61583333334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45147</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45603</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>45601</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45805</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45805</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>44896</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45093</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>44903</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45313</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>44698</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45469</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45716</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45621.595</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45408</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45757.4546875</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44910</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45586</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>45442</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45316</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45320</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>44789</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45117</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45226</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>44909</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45140</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45107</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>45226</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>45740</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45245</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45687</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45035</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45223</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>45428</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45603</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45849</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45279</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45561</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45713.54880787037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45849</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45261</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45393</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>44719</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>44851</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44943</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38665,7 +38665,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>45307</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45618</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44550</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45488</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45251</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>44637</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>45691</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>44911</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>45247</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44915</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>45545</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45819</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45124</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44830</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45135</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>44900</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45735.42790509259</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45735.4485300926</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45239</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44924</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45611.49162037037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45713</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44887</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>45279</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>44761</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45182</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45530</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45530</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44561,7 +44561,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45041</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44923,7 +44923,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45320</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45078</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45239</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>44522</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45544</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45117</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44062</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>44383</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>44952</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45663</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45271</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48444,7 +48444,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48739,7 +48739,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48801,7 +48801,7 @@
         <v>44620</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>44894</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>45813</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45881.63590277778</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45881.6677199074</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>45881.67791666667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45468</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45880</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45740</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>44875</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45881.40667824074</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45371</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>44735</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>44847</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51997,7 +51997,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45772</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>45883.49055555555</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>45883.51207175926</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52540,7 +52540,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45882.30746527778</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45142</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>44501</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>44830</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>44603</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>44424</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45205</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53601,7 +53601,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>44641</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45006.49</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>44874</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>44890</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45226</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -54129,7 +54129,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>44981</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54310,7 +54310,7 @@
         <v>45561</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>44735</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45107</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>45266</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45281</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>44323</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>44826</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54771,7 +54771,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54833,7 +54833,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>44369</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54957,7 +54957,7 @@
         <v>44580</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -55014,7 +55014,7 @@
         <v>45694</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>44491</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -55190,7 +55190,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>44881</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55495,7 +55495,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55557,7 +55557,7 @@
         <v>44933</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55614,7 +55614,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55785,7 +55785,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55847,7 +55847,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -56152,7 +56152,7 @@
         <v>44994</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -56209,7 +56209,7 @@
         <v>44952</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45015</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>45223</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45058</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45020</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45457</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45457</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56809,7 +56809,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -57047,7 +57047,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>44900</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57280,7 +57280,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57337,7 +57337,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>45103</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45103</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57642,7 +57642,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>45142</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57766,7 +57766,7 @@
         <v>45616</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57952,7 +57952,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -58009,7 +58009,7 @@
         <v>44952</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -58128,7 +58128,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -58185,7 +58185,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58242,7 +58242,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58304,7 +58304,7 @@
         <v>45672</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58361,7 +58361,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58418,7 +58418,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45713.36498842593</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>45271</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>44733</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -59023,7 +59023,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -59085,7 +59085,7 @@
         <v>45681</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -59204,7 +59204,7 @@
         <v>44603</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59261,7 +59261,7 @@
         <v>45097</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59323,7 +59323,7 @@
         <v>45238</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59504,7 +59504,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>45041</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>45154</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>44735</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>45701</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59866,7 +59866,7 @@
         <v>45462</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59923,7 +59923,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59980,7 +59980,7 @@
         <v>45156</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>45149</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -60099,7 +60099,7 @@
         <v>45599</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60342,7 +60342,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60404,7 +60404,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45541</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60528,7 +60528,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60590,7 +60590,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60652,7 +60652,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60714,7 +60714,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60828,7 +60828,7 @@
         <v>45187</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60890,7 +60890,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60947,7 +60947,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -61004,7 +61004,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -61066,7 +61066,7 @@
         <v>45176</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>44812</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61309,7 +61309,7 @@
         <v>44529</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>45503</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61542,7 +61542,7 @@
         <v>45666</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61661,7 +61661,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61723,7 +61723,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61785,7 +61785,7 @@
         <v>44403</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61842,7 +61842,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61899,7 +61899,7 @@
         <v>44820</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61956,7 +61956,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -62080,7 +62080,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -62142,7 +62142,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -62204,7 +62204,7 @@
         <v>45091</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62266,7 +62266,7 @@
         <v>44907</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62323,7 +62323,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62385,7 +62385,7 @@
         <v>44924</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62442,7 +62442,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62504,7 +62504,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>44826</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62804,7 +62804,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45176</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62985,7 +62985,7 @@
         <v>45279</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -63166,7 +63166,7 @@
         <v>45063</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>44874</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63285,7 +63285,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>45775</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63404,7 +63404,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>45751</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63523,7 +63523,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63585,7 +63585,7 @@
         <v>45594</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63647,7 +63647,7 @@
         <v>45593</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63709,7 +63709,7 @@
         <v>44670</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63766,7 +63766,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63828,7 +63828,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63947,7 +63947,7 @@
         <v>45155</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45635</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -64066,7 +64066,7 @@
         <v>45308</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -64128,7 +64128,7 @@
         <v>45583</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64185,7 +64185,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         <v>45070.66266203704</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64309,7 +64309,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45107</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64433,7 +64433,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         <v>44083</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64552,7 +64552,7 @@
         <v>45211</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64614,7 +64614,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64738,7 +64738,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64800,7 +64800,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>45709</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64971,7 +64971,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>44620</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -65090,7 +65090,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -65147,7 +65147,7 @@
         <v>45101</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65204,7 +65204,7 @@
         <v>44642</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65261,7 +65261,7 @@
         <v>44963</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65318,7 +65318,7 @@
         <v>45098</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65375,7 +65375,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65494,7 +65494,7 @@
         <v>45233</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>45219</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65613,7 +65613,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65675,7 +65675,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65737,7 +65737,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65851,7 +65851,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65913,7 +65913,7 @@
         <v>45091</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65975,7 +65975,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -66032,7 +66032,7 @@
         <v>44823</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -66094,7 +66094,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -66151,7 +66151,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66213,7 +66213,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66275,7 +66275,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45103</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66389,7 +66389,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66446,7 +66446,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66503,7 +66503,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66565,7 +66565,7 @@
         <v>44876</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>44477</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66684,7 +66684,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66741,7 +66741,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66798,7 +66798,7 @@
         <v>45615</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66860,7 +66860,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66917,7 +66917,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66979,7 +66979,7 @@
         <v>45076</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -67036,7 +67036,7 @@
         <v>44980</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -67093,7 +67093,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -67155,7 +67155,7 @@
         <v>45595</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67217,7 +67217,7 @@
         <v>45701</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67274,7 +67274,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67331,7 +67331,7 @@
         <v>45364</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67388,7 +67388,7 @@
         <v>44466</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67445,7 +67445,7 @@
         <v>45406</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67502,7 +67502,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67564,7 +67564,7 @@
         <v>45588</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67621,7 +67621,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67683,7 +67683,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67745,7 +67745,7 @@
         <v>45732</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -67802,7 +67802,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67921,7 +67921,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67983,7 +67983,7 @@
         <v>45555</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -68040,7 +68040,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -68102,7 +68102,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -68164,7 +68164,7 @@
         <v>45174</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68226,7 +68226,7 @@
         <v>44903</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68288,7 +68288,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68345,7 +68345,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68407,7 +68407,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68464,7 +68464,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68588,7 +68588,7 @@
         <v>45155</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68650,7 +68650,7 @@
         <v>45279</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68707,7 +68707,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -68769,7 +68769,7 @@
         <v>45373</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -68826,7 +68826,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -68888,7 +68888,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>44886</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -69069,7 +69069,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -69126,7 +69126,7 @@
         <v>45271</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69183,7 +69183,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69245,7 +69245,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69307,7 +69307,7 @@
         <v>45101</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69364,7 +69364,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69426,7 +69426,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -69483,7 +69483,7 @@
         <v>44909</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -69545,7 +69545,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -69607,7 +69607,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -69669,7 +69669,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -69731,7 +69731,7 @@
         <v>45546</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -69788,7 +69788,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -69845,7 +69845,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -69907,7 +69907,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -69969,7 +69969,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -70031,7 +70031,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45887.46398148148</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>45488</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>44433</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45217</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>45877.46135416667</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>44902</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45798</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>45161</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44103</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45152</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45672</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>44820</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44132</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>44412</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45624</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44980</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44749</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44433</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45589</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45890.44530092592</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44501</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45590</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45618</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45231</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45300</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45887.62298611111</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>45558.44512731482</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>44601</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>44501</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45103</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>45695</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45572.42619212963</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45363</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44902</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45877.56935185185</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45887.42761574074</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>45560.43387731481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45016</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44615</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>44494</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44616</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>44795</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44795</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45602</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45470</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45595</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>45579</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45299</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45791.57008101852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45595</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45798</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45463</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>45231</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45622</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45594</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45251</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>44543</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44897</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45881.41111111111</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45889.29927083333</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45889.40121527778</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44376</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44081</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44147</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44386</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>44403</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44495</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44426</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44095</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>44585</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>44120</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44148</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44469</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44403</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>44874</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44711</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44475</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44784</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>44120</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44407</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44405</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44109</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>44105</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44067</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44490</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44354</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>44839</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>44777</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>44805</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44564</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>44439</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>44742</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44805</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44515</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>44109</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44201</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44183</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44459</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>44846</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44481</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44123</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>44704</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>44551</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>44726</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44544</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44454</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44496</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44513</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>44358</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44760</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44558</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>44484</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>44484</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44749</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>44277</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>44123</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44102</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>44837</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>44182</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44809</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44875</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44429</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44531</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44433</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44469</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44095</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44120</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44282</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44439</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44509</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44277</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44673</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44537</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>44670</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>44903</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>44545</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45457</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44182</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44182</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44880</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44901</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44846</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>44847</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45415</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45155</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45713.36498842593</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45098</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>45615</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>44915</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44909</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44603</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45176</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45279</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45616</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45455</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45663</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>45772</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44952</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45271</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45097</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>44083</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>44383</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>44826</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44820</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45576</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45604</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45561</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45020</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45583</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45187</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45015</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45775</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44158</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>44894</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45561</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45075</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45075</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45705</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45219</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45103</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44788</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44874</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45135</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44550</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45378</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45142</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44091</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45103</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45107</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45107</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44719</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45176</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>44603</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45393</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45681</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>44698</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>44761</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44901</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44963</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45211</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44323</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45546</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45251</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45618</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45091</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45313</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45320</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45751</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>45468</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45603</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>45328</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45672</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44874</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>44876</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45735.4485300926</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44909</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45320</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>44851</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45238</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45545</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
         <v>45035</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44369</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45408</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45701</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44896</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45503</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44735</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44120</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45779</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45457</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45783.45171296296</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44952</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45611.49162037037</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45182</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>44830</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45279</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45694</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>44642</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45595</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>44412</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45786</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45266</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45789</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45371</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45786.53510416667</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45271</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45280</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44571</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45560.34431712963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45140</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45786.49009259259</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45541</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45149</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38952,7 +38952,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45014</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45063</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>44581</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45555</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>45600</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45790.61496527777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45041</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>44924</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>44733</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45796</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44812</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45124</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>44440</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45457</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44910</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45453</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45281</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45687</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45442</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45798</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45135</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>44820</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44566</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45040</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45544</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45428</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45586</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>44886</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45223</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45469</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45798</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45308</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45281</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45174</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>45805</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>45805</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44735</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -46318,7 +46318,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45621.595</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45588</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45364</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45147</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45155</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47518,7 +47518,7 @@
         <v>45462</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47637,7 +47637,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45373</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>45041</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>44501</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45205</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>45117</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45239</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45154</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>45223</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45316</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45279</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45226</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>44826</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>44924</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45713.54880787037</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>44980</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45223</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>44403</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -50156,7 +50156,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45594</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45691</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45261</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45307</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>44900</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45378</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45815</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>44981</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>44887</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51413,7 +51413,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>44641</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45819</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45107</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -52028,7 +52028,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45103</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>45488</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>44826</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>44943</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52690,7 +52690,7 @@
         <v>44830</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52804,7 +52804,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52866,7 +52866,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -53342,7 +53342,7 @@
         <v>45701</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53399,7 +53399,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>44900</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45820</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53632,7 +53632,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53694,7 +53694,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45245</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45226</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54842,7 +54842,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54904,7 +54904,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54966,7 +54966,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -55028,7 +55028,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -55152,7 +55152,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -55209,7 +55209,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -55266,7 +55266,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55504,7 +55504,7 @@
         <v>44908</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>44735</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45233</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>45117</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55861,7 +55861,7 @@
         <v>44875</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55923,7 +55923,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -56166,7 +56166,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>44491</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56595,7 +56595,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45239</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>44890</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -57262,7 +57262,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>45093</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57805,7 +57805,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57929,7 +57929,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57991,7 +57991,7 @@
         <v>45101</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -58048,7 +58048,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>44952</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58534,7 +58534,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58658,7 +58658,7 @@
         <v>45599</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58720,7 +58720,7 @@
         <v>44522</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58782,7 +58782,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58839,7 +58839,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>45058</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -59020,7 +59020,7 @@
         <v>44466</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -59191,7 +59191,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>44637</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45145</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59610,7 +59610,7 @@
         <v>45142</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59672,7 +59672,7 @@
         <v>45226</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59729,7 +59729,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>45271</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59967,7 +59967,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>44933</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -60267,7 +60267,7 @@
         <v>45393</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -60329,7 +60329,7 @@
         <v>44909</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -60391,7 +60391,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60453,7 +60453,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60634,7 +60634,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60696,7 +60696,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60991,7 +60991,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -61110,7 +61110,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -61172,7 +61172,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -61229,7 +61229,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>45006.49</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>44496</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61410,7 +61410,7 @@
         <v>45454</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61467,7 +61467,7 @@
         <v>45813</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61524,7 +61524,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61581,7 +61581,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61767,7 +61767,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61824,7 +61824,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61948,7 +61948,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -62129,7 +62129,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45603</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45880</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -62367,7 +62367,7 @@
         <v>45881.63590277778</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45881.6677199074</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62491,7 +62491,7 @@
         <v>45663</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62548,7 +62548,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62915,7 +62915,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62977,7 +62977,7 @@
         <v>45881.40667824074</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -63039,7 +63039,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -63163,7 +63163,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -63334,7 +63334,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>45881.67791666667</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63520,7 +63520,7 @@
         <v>45281</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63577,7 +63577,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63691,7 +63691,7 @@
         <v>44823</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63753,7 +63753,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63815,7 +63815,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63872,7 +63872,7 @@
         <v>44620</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -64115,7 +64115,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -64239,7 +64239,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -64296,7 +64296,7 @@
         <v>44881</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64586,7 +64586,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>44424</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64705,7 +64705,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64762,7 +64762,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64824,7 +64824,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64886,7 +64886,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64948,7 +64948,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>45554</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -65072,7 +65072,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -65196,7 +65196,7 @@
         <v>45887.42543981481</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -65258,7 +65258,7 @@
         <v>45887.67797453704</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -65320,7 +65320,7 @@
         <v>44789</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>45887.6322337963</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65444,7 +65444,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65568,7 +65568,7 @@
         <v>45887.43675925926</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65692,7 +65692,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>45279</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65806,7 +65806,7 @@
         <v>45883.49055555555</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>45883.51207175926</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>45560.34564814815</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65987,7 +65987,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>45156</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -66111,7 +66111,7 @@
         <v>45887.62902777778</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -66173,7 +66173,7 @@
         <v>45070.66266203704</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -66235,7 +66235,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -66297,7 +66297,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -66354,7 +66354,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66411,7 +66411,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66473,7 +66473,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         <v>45373</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66592,7 +66592,7 @@
         <v>45882.30746527778</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66649,7 +66649,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66711,7 +66711,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66835,7 +66835,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66897,7 +66897,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66959,7 +66959,7 @@
         <v>45076</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -67016,7 +67016,7 @@
         <v>45888.60806712963</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -67078,7 +67078,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -67140,7 +67140,7 @@
         <v>45601</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -67197,7 +67197,7 @@
         <v>45889.67865740741</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>45713</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -67373,7 +67373,7 @@
         <v>45888.31405092592</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67435,7 +67435,7 @@
         <v>45889.67777777778</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67497,7 +67497,7 @@
         <v>45889.67834490741</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67559,7 +67559,7 @@
         <v>45889.82722222222</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67621,7 +67621,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67683,7 +67683,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67745,7 +67745,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67802,7 +67802,7 @@
         <v>45740</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67864,7 +67864,7 @@
         <v>45889.33643518519</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67926,7 +67926,7 @@
         <v>45363</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67988,7 +67988,7 @@
         <v>45889.34109953704</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -68050,7 +68050,7 @@
         <v>44994</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -68107,7 +68107,7 @@
         <v>45888.59356481482</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -68169,7 +68169,7 @@
         <v>45888.63608796296</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -68231,7 +68231,7 @@
         <v>45888.59829861111</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -68293,7 +68293,7 @@
         <v>45889.52583333333</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -68355,7 +68355,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -68417,7 +68417,7 @@
         <v>45732</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68474,7 +68474,7 @@
         <v>45101</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68531,7 +68531,7 @@
         <v>45740</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68593,7 +68593,7 @@
         <v>45635</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68650,7 +68650,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68707,7 +68707,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68764,7 +68764,7 @@
         <v>44909</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68826,7 +68826,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68888,7 +68888,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>45530</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>45530</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -69069,7 +69069,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -69131,7 +69131,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -69193,7 +69193,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -69255,7 +69255,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -69317,7 +69317,7 @@
         <v>45890</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -69374,7 +69374,7 @@
         <v>45890</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69431,7 +69431,7 @@
         <v>45890.45545138889</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69493,7 +69493,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69555,7 +69555,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69617,7 +69617,7 @@
         <v>45890.46518518519</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69679,7 +69679,7 @@
         <v>45849</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -69736,7 +69736,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -69798,7 +69798,7 @@
         <v>45890.42685185185</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -69860,7 +69860,7 @@
         <v>45890.47592592592</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -69922,7 +69922,7 @@
         <v>44620</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -69979,7 +69979,7 @@
         <v>45890.43667824074</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -70041,7 +70041,7 @@
         <v>45890.35861111111</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -70165,7 +70165,7 @@
         <v>45891</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -70222,7 +70222,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -70284,7 +70284,7 @@
         <v>45849</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -70341,7 +70341,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -70403,7 +70403,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -70465,7 +70465,7 @@
         <v>45890.61520833334</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -70589,7 +70589,7 @@
         <v>45406</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -70646,7 +70646,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -70703,7 +70703,7 @@
         <v>45079</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -70760,7 +70760,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -70822,7 +70822,7 @@
         <v>45021</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -70879,7 +70879,7 @@
         <v>45666</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -70936,7 +70936,7 @@
         <v>44903</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -70998,7 +70998,7 @@
         <v>44580</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -71055,7 +71055,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -71117,7 +71117,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -71174,7 +71174,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -71236,7 +71236,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -71293,7 +71293,7 @@
         <v>45593</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -71355,7 +71355,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -71417,7 +71417,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -71479,7 +71479,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -71536,7 +71536,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C1103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -71598,7 +71598,7 @@
         <v>45716</v>
       </c>
       <c r="C1104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -71655,7 +71655,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C1105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -71712,7 +71712,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C1106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -71769,7 +71769,7 @@
         <v>45709</v>
       </c>
       <c r="C1107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45887.46398148148</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>45488</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>44433</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45217</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>45877.46135416667</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>44902</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45798</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>45161</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44103</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45152</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45672</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>44820</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44132</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>44412</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45624</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44980</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44749</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44433</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45589</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45890.44530092592</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44501</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45590</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45618</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45231</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45300</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45887.62298611111</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>45558.44512731482</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>44601</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>44501</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45103</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>45695</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45572.42619212963</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45363</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44902</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45877.56935185185</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45887.42761574074</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>45560.43387731481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45016</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44615</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>44494</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44616</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>44795</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44795</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45602</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45470</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45595</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>45579</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45299</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45791.57008101852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45595</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45798</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45463</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>45231</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45622</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45594</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45251</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>44543</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44897</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45881.41111111111</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45889.29927083333</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45889.40121527778</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44376</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44081</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44147</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44386</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>44403</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44495</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44426</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44095</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>44585</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>44120</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44148</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44469</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44403</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>44874</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44711</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44475</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44784</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>44120</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44407</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44405</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44109</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>44105</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44067</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44490</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44354</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>44839</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>44777</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>44805</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44564</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>44439</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>44742</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44805</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44515</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>44109</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44201</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44183</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44459</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>44846</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44481</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44123</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>44704</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>44551</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>44726</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44544</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44454</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44496</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44513</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>44358</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44760</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44558</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>44484</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>44484</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44749</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>44277</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>44123</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44102</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>44837</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>44182</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44809</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44875</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44429</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44531</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44433</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44469</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44095</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44120</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44282</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44439</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44509</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44277</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44673</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44537</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>44670</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>44903</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>44545</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45457</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44182</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44182</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44880</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44901</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44846</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>44847</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45415</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45155</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45713.36498842593</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45098</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>45615</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>44915</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44909</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44603</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45176</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45279</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45616</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45455</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45663</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>45772</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44952</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45271</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45097</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>44083</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>44383</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>44826</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44820</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45576</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45604</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45561</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45020</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45583</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45187</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45015</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45775</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44158</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>44894</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45561</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45075</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45075</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45705</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45219</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45103</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44788</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44874</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45135</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44550</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45378</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45142</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44091</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45103</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45107</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45107</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44719</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45176</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>44603</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45393</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45681</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>44698</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>44761</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44901</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44963</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45211</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44323</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45546</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45251</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45618</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45091</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45313</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45320</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45751</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>45468</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45603</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>45328</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45672</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44874</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>44876</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45735.4485300926</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44909</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45320</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>44851</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45238</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45545</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
         <v>45035</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44369</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45408</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45701</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44896</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45503</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44735</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44120</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45779</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45457</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45783.45171296296</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44952</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45611.49162037037</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45182</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>44830</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45279</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45694</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>44642</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45595</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>44412</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45786</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45266</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45789</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45371</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45786.53510416667</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45271</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45280</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44571</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45560.34431712963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45140</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45786.49009259259</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45541</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45149</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38952,7 +38952,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45014</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45063</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>44581</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45555</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>45600</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45790.61496527777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45041</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>44924</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>44733</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45796</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44812</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45124</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>44440</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45457</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44910</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45453</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45281</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45687</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45442</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45798</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45135</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>44820</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44566</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45040</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45544</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45428</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45586</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>44886</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45223</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45469</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45798</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45308</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45281</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45174</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>45805</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>45805</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44735</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -46318,7 +46318,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45621.595</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45588</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45364</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45147</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45155</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47518,7 +47518,7 @@
         <v>45462</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47637,7 +47637,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45373</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>45041</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>44501</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45205</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>45117</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45239</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45154</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>45223</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45316</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45279</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45226</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>44826</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>44924</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45713.54880787037</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>44980</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45223</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>44403</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -50156,7 +50156,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45594</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45691</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45261</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45307</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>44900</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45378</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45815</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>44981</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>44887</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51413,7 +51413,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>44641</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45819</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45107</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -52028,7 +52028,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45103</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>45488</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>44826</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>44943</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52690,7 +52690,7 @@
         <v>44830</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52804,7 +52804,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52866,7 +52866,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -53342,7 +53342,7 @@
         <v>45701</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53399,7 +53399,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>44900</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45820</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53632,7 +53632,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53694,7 +53694,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45245</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45226</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54842,7 +54842,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54904,7 +54904,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54966,7 +54966,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -55028,7 +55028,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -55152,7 +55152,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -55209,7 +55209,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -55266,7 +55266,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55504,7 +55504,7 @@
         <v>44908</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>44735</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45233</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>45117</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55861,7 +55861,7 @@
         <v>44875</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55923,7 +55923,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -56166,7 +56166,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>44491</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56595,7 +56595,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45239</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>44890</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -57262,7 +57262,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>45093</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57805,7 +57805,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57929,7 +57929,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57991,7 +57991,7 @@
         <v>45101</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -58048,7 +58048,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>44952</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58534,7 +58534,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58658,7 +58658,7 @@
         <v>45599</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58720,7 +58720,7 @@
         <v>44522</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58782,7 +58782,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58839,7 +58839,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>45058</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -59020,7 +59020,7 @@
         <v>44466</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -59191,7 +59191,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>44637</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45145</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59610,7 +59610,7 @@
         <v>45142</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59672,7 +59672,7 @@
         <v>45226</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59729,7 +59729,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>45271</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59967,7 +59967,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>44933</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -60267,7 +60267,7 @@
         <v>45393</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -60329,7 +60329,7 @@
         <v>44909</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -60391,7 +60391,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60453,7 +60453,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60634,7 +60634,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60696,7 +60696,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60991,7 +60991,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -61110,7 +61110,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -61172,7 +61172,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -61229,7 +61229,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>45006.49</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>44496</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61410,7 +61410,7 @@
         <v>45454</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61467,7 +61467,7 @@
         <v>45813</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61524,7 +61524,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61581,7 +61581,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61767,7 +61767,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61824,7 +61824,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61948,7 +61948,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -62129,7 +62129,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45603</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45880</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -62367,7 +62367,7 @@
         <v>45881.63590277778</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45881.6677199074</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62491,7 +62491,7 @@
         <v>45663</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62548,7 +62548,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62915,7 +62915,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62977,7 +62977,7 @@
         <v>45881.40667824074</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -63039,7 +63039,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -63163,7 +63163,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -63334,7 +63334,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>45881.67791666667</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63520,7 +63520,7 @@
         <v>45281</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63577,7 +63577,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63691,7 +63691,7 @@
         <v>44823</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63753,7 +63753,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63815,7 +63815,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63872,7 +63872,7 @@
         <v>44620</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -64115,7 +64115,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -64239,7 +64239,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -64296,7 +64296,7 @@
         <v>44881</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64586,7 +64586,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>44424</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64705,7 +64705,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64762,7 +64762,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64824,7 +64824,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64886,7 +64886,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64948,7 +64948,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>45554</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -65072,7 +65072,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -65196,7 +65196,7 @@
         <v>45887.42543981481</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -65258,7 +65258,7 @@
         <v>45887.67797453704</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -65320,7 +65320,7 @@
         <v>44789</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>45887.6322337963</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65444,7 +65444,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65568,7 +65568,7 @@
         <v>45887.43675925926</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65692,7 +65692,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>45279</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65806,7 +65806,7 @@
         <v>45883.49055555555</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>45883.51207175926</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>45560.34564814815</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65987,7 +65987,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>45156</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -66111,7 +66111,7 @@
         <v>45887.62902777778</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -66173,7 +66173,7 @@
         <v>45070.66266203704</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -66235,7 +66235,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -66297,7 +66297,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -66354,7 +66354,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66411,7 +66411,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66473,7 +66473,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         <v>45373</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66592,7 +66592,7 @@
         <v>45882.30746527778</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66649,7 +66649,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66711,7 +66711,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66835,7 +66835,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66897,7 +66897,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66959,7 +66959,7 @@
         <v>45076</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -67016,7 +67016,7 @@
         <v>45888.60806712963</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -67078,7 +67078,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -67140,7 +67140,7 @@
         <v>45601</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -67197,7 +67197,7 @@
         <v>45889.67865740741</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>45713</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -67373,7 +67373,7 @@
         <v>45888.31405092592</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67435,7 +67435,7 @@
         <v>45889.67777777778</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67497,7 +67497,7 @@
         <v>45889.67834490741</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67559,7 +67559,7 @@
         <v>45889.82722222222</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67621,7 +67621,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67683,7 +67683,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67745,7 +67745,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67802,7 +67802,7 @@
         <v>45740</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67864,7 +67864,7 @@
         <v>45889.33643518519</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67926,7 +67926,7 @@
         <v>45363</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67988,7 +67988,7 @@
         <v>45889.34109953704</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -68050,7 +68050,7 @@
         <v>44994</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -68107,7 +68107,7 @@
         <v>45888.59356481482</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -68169,7 +68169,7 @@
         <v>45888.63608796296</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -68231,7 +68231,7 @@
         <v>45888.59829861111</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -68293,7 +68293,7 @@
         <v>45889.52583333333</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -68355,7 +68355,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -68417,7 +68417,7 @@
         <v>45732</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68474,7 +68474,7 @@
         <v>45101</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68531,7 +68531,7 @@
         <v>45740</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68593,7 +68593,7 @@
         <v>45635</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68650,7 +68650,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68707,7 +68707,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68764,7 +68764,7 @@
         <v>44909</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68826,7 +68826,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68888,7 +68888,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>45530</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>45530</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -69069,7 +69069,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -69131,7 +69131,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -69193,7 +69193,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -69255,7 +69255,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -69317,7 +69317,7 @@
         <v>45890</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -69374,7 +69374,7 @@
         <v>45890</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69431,7 +69431,7 @@
         <v>45890.45545138889</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69493,7 +69493,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69555,7 +69555,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69617,7 +69617,7 @@
         <v>45890.46518518519</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69679,7 +69679,7 @@
         <v>45849</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -69736,7 +69736,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -69798,7 +69798,7 @@
         <v>45890.42685185185</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -69860,7 +69860,7 @@
         <v>45890.47592592592</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -69922,7 +69922,7 @@
         <v>44620</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -69979,7 +69979,7 @@
         <v>45890.43667824074</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -70041,7 +70041,7 @@
         <v>45890.35861111111</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -70165,7 +70165,7 @@
         <v>45891</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -70222,7 +70222,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -70284,7 +70284,7 @@
         <v>45849</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -70341,7 +70341,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -70403,7 +70403,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -70465,7 +70465,7 @@
         <v>45890.61520833334</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -70589,7 +70589,7 @@
         <v>45406</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -70646,7 +70646,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -70703,7 +70703,7 @@
         <v>45079</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -70760,7 +70760,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -70822,7 +70822,7 @@
         <v>45021</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -70879,7 +70879,7 @@
         <v>45666</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -70936,7 +70936,7 @@
         <v>44903</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -70998,7 +70998,7 @@
         <v>44580</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -71055,7 +71055,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -71117,7 +71117,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -71174,7 +71174,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -71236,7 +71236,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -71293,7 +71293,7 @@
         <v>45593</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -71355,7 +71355,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -71417,7 +71417,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -71479,7 +71479,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -71536,7 +71536,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C1103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -71598,7 +71598,7 @@
         <v>45716</v>
       </c>
       <c r="C1104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -71655,7 +71655,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C1105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -71712,7 +71712,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C1106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -71769,7 +71769,7 @@
         <v>45709</v>
       </c>
       <c r="C1107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45887.46398148148</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>45488</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>44433</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45877.46135416667</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>44902</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45217</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45798</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44103</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45161</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45672</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45152</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>44820</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44132</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>44412</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45624</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44980</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44749</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44433</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45589</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45890.44530092592</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44501</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45300</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45887.62298611111</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45590</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45618</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44601</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44501</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45103</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>45411</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>44902</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45363</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45877.56935185185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>45887.42761574074</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45572.42619212963</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45016</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>45695</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45560.43387731481</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44615</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>44494</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44616</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>44795</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44795</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45299</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44543</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45791.57008101852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45470</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45798</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45622</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45595</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>45594</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45231</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>44897</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45881.41111111111</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45889.40121527778</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>45889.29927083333</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45251</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45602</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45579</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45595</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>44376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>44081</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44147</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44386</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44495</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44403</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44426</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>44095</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44585</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44148</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44120</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44469</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>44403</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>44874</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44354</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44711</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>44784</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>44120</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44407</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44405</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44109</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>44105</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>44490</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>44839</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>44777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44761</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>44805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44564</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>44439</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>44742</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44711</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>44805</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44515</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44109</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>44201</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>44183</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44459</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44123</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>44551</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44544</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44726</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44454</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>44358</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44496</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44760</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44513</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44558</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44484</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>44484</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44749</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>44277</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>44837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>44809</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44102</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>44123</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>44429</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44875</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44433</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44469</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44182</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44509</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>44531</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44277</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44673</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>44095</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>44282</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>44439</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>44120</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>44545</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44537</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>44182</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44182</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44704</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>44846</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45378</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44826</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>44820</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45135</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45600</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45363</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45079</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45455</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45373</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>44901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44120</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45779</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45281</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45393</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44091</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>44909</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45378</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44158</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44908</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45783.45171296296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45280</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>44880</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45786.49009259259</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>44896</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45786</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44903</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45021</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45560.34564814815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45469</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>45281</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>44412</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45786.53510416667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45408</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45040</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44910</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>45586</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45442</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45320</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45014</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45790.61496527777</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45789</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45226</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44909</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44909</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45140</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>44496</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45145</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>45454</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45245</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>44581</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45035</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44910</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45796</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44440</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45428</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45457</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45560.34431712963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45576</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45453</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45561</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45798</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>45393</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45798</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>44851</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>44943</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45604</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45307</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>45618</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44550</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45415</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44637</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44911</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44915</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45805</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45805</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45545</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45621.595</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45147</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45316</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>45603</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45601</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>45223</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45663</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44924</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45093</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45279</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45611.49162037037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45713.54880787037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45313</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>44698</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45716</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45182</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45815</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45488</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>45041</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>44571</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45320</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45691</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45544</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>44789</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39395,7 +39395,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45247</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45819</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>45117</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45820</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45117</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44383</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>44952</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45663</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45107</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45226</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45740</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41624,7 +41624,7 @@
         <v>45371</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45687</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>44735</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45772</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45142</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45205</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>45261</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>44641</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45006.49</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>44719</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45226</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45251</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>44981</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>44735</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>45281</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>45124</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45694</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>44491</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>44830</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45135</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>44900</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>44933</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45881.63590277778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45881.6677199074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45881.67791666667</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>45239</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>44994</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44952</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45880</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>45881.40667824074</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45713</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>44887</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45279</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49367,7 +49367,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>44761</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45530</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45530</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45883.49055555555</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45883.51207175926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>45882.30746527778</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45078</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45239</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>44522</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45888.60806712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45887.43675925926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50924,7 +50924,7 @@
         <v>45457</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45457</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45888.31405092592</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45887.6322337963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51472,7 +51472,7 @@
         <v>45887.42543981481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45888.63608796296</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>44900</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45887.62902777778</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45888.59356481482</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45888.59829861111</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45142</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>45616</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45887.67797453704</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45890.35861111111</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45889.67865740741</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45890</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>45890</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         <v>45890.45545138889</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45889.52583333333</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>45890.61520833334</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53783,7 +53783,7 @@
         <v>45889.82722222222</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>45672</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53959,7 +53959,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -54021,7 +54021,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>45713.36498842593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>45890.42685185185</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>45889.33643518519</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>45890.46518518519</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>45890.47592592592</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -54393,7 +54393,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45889.34109953704</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45889.67777777778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>45889.67834490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45890.43667824074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>45271</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54760,7 +54760,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54884,7 +54884,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45849</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>44733</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>45894</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45681</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -55355,7 +55355,7 @@
         <v>45849</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45894.4565162037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>45891</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>45271</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55774,7 +55774,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55836,7 +55836,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55960,7 +55960,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -56265,7 +56265,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45895.46971064815</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>44620</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56694,7 +56694,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>44735</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45701</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45896.60385416666</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45705</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>44894</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45896.63950231481</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57542,7 +57542,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>44861</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45468</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57842,7 +57842,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57899,7 +57899,7 @@
         <v>45897.38390046296</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>45897.37753472223</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>45740</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>44875</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -58385,7 +58385,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58504,7 +58504,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58566,7 +58566,7 @@
         <v>45813</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>45898.37825231482</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>45898.43600694444</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -59052,7 +59052,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>44847</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -59233,7 +59233,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -59295,7 +59295,7 @@
         <v>45187</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         <v>44812</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59652,7 +59652,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59709,7 +59709,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>44501</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45666</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59890,7 +59890,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -60014,7 +60014,7 @@
         <v>44830</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         <v>44403</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -60128,7 +60128,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -60185,7 +60185,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -60242,7 +60242,7 @@
         <v>44820</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>44907</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>44603</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
         <v>44424</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         <v>44826</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60537,7 +60537,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60594,7 +60594,7 @@
         <v>45176</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60651,7 +60651,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>45279</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>44874</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60827,7 +60827,7 @@
         <v>44874</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60889,7 +60889,7 @@
         <v>45775</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>44890</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>44670</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -61360,7 +61360,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61422,7 +61422,7 @@
         <v>45561</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>45107</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61541,7 +61541,7 @@
         <v>45107</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61660,7 +61660,7 @@
         <v>45266</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>44083</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>44323</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>44826</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>44369</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>44580</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -62131,7 +62131,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -62188,7 +62188,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45709</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -62302,7 +62302,7 @@
         <v>44620</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>44881</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>44642</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>44963</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62768,7 +62768,7 @@
         <v>45098</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62825,7 +62825,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62944,7 +62944,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -63006,7 +63006,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>45015</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -63239,7 +63239,7 @@
         <v>45091</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>44823</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63363,7 +63363,7 @@
         <v>45223</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63420,7 +63420,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45103</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45058</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>44876</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>44477</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>45020</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45701</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>44466</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -64119,7 +64119,7 @@
         <v>45406</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -64176,7 +64176,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -64238,7 +64238,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64295,7 +64295,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45732</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64595,7 +64595,7 @@
         <v>45555</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64652,7 +64652,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64714,7 +64714,7 @@
         <v>44903</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64838,7 +64838,7 @@
         <v>44952</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64957,7 +64957,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -65019,7 +65019,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -65081,7 +65081,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -65262,7 +65262,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65324,7 +65324,7 @@
         <v>44886</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65443,7 +65443,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65505,7 +65505,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>44603</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>45271</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65681,7 +65681,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>45101</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65862,7 +65862,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65924,7 +65924,7 @@
         <v>45097</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65986,7 +65986,7 @@
         <v>45238</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -66043,7 +66043,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -66105,7 +66105,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -66167,7 +66167,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -66229,7 +66229,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -66286,7 +66286,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>45041</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45462</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66524,7 +66524,7 @@
         <v>45156</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45599</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66648,7 +66648,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66710,7 +66710,7 @@
         <v>45541</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66772,7 +66772,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66834,7 +66834,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -67010,7 +67010,7 @@
         <v>45176</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -67067,7 +67067,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -67129,7 +67129,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -67191,7 +67191,7 @@
         <v>44529</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -67248,7 +67248,7 @@
         <v>45503</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -67305,7 +67305,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67367,7 +67367,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67429,7 +67429,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67491,7 +67491,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67553,7 +67553,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67615,7 +67615,7 @@
         <v>45091</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67677,7 +67677,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67739,7 +67739,7 @@
         <v>44924</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67796,7 +67796,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67858,7 +67858,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67915,7 +67915,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -67977,7 +67977,7 @@
         <v>45328</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -68034,7 +68034,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -68096,7 +68096,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -68158,7 +68158,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -68220,7 +68220,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -68282,7 +68282,7 @@
         <v>45063</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -68339,7 +68339,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68401,7 +68401,7 @@
         <v>45751</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68463,7 +68463,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68525,7 +68525,7 @@
         <v>45594</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68587,7 +68587,7 @@
         <v>45593</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68649,7 +68649,7 @@
         <v>45155</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68711,7 +68711,7 @@
         <v>45635</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68768,7 +68768,7 @@
         <v>45308</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68830,7 +68830,7 @@
         <v>45583</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68887,7 +68887,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -68949,7 +68949,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -69011,7 +69011,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -69073,7 +69073,7 @@
         <v>45211</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -69135,7 +69135,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -69197,7 +69197,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -69259,7 +69259,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -69321,7 +69321,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69378,7 +69378,7 @@
         <v>45101</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69435,7 +69435,7 @@
         <v>45233</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69492,7 +69492,7 @@
         <v>45219</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69554,7 +69554,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69616,7 +69616,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -69673,7 +69673,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -69735,7 +69735,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -69797,7 +69797,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -69911,7 +69911,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -69973,7 +69973,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -70030,7 +70030,7 @@
         <v>45615</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -70092,7 +70092,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -70149,7 +70149,7 @@
         <v>44980</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -70206,7 +70206,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -70268,7 +70268,7 @@
         <v>45595</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -70330,7 +70330,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -70387,7 +70387,7 @@
         <v>45364</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -70444,7 +70444,7 @@
         <v>45588</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -70501,7 +70501,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -70558,7 +70558,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -70620,7 +70620,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -70682,7 +70682,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -70744,7 +70744,7 @@
         <v>45174</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -70806,7 +70806,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -70863,7 +70863,7 @@
         <v>45155</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -70925,7 +70925,7 @@
         <v>45279</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -70982,7 +70982,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -71044,7 +71044,7 @@
         <v>45373</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -71101,7 +71101,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -71163,7 +71163,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -71225,7 +71225,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -71282,7 +71282,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -71339,7 +71339,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -71396,7 +71396,7 @@
         <v>44909</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -71458,7 +71458,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C1103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -71520,7 +71520,7 @@
         <v>45546</v>
       </c>
       <c r="C1104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -71577,7 +71577,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C1105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -71639,7 +71639,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C1106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -71701,7 +71701,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C1107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45887.46398148148</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>45488</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>44433</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45877.46135416667</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>44902</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45217</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45798</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44103</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45161</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45672</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45152</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>44820</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44132</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>44412</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45624</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44980</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44749</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44433</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45589</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45890.44530092592</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44501</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45300</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45887.62298611111</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45590</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45618</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44601</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44501</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45103</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>45411</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>44902</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45363</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45877.56935185185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>45887.42761574074</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45572.42619212963</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45016</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>45695</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45560.43387731481</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44615</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>44494</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44616</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>44795</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44795</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45299</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44543</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45791.57008101852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45470</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45798</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45622</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45595</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>45594</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45231</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>44897</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45881.41111111111</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45889.40121527778</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>45889.29927083333</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45251</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45602</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45579</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45595</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>44376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>44081</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44147</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44386</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44495</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44403</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44426</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>44095</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44585</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44148</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44120</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44469</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>44403</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>44874</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44354</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44711</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>44784</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>44120</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44407</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44405</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44109</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>44105</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>44490</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>44839</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>44777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44761</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>44805</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44564</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>44439</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>44742</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44711</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>44805</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44515</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44109</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>44201</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>44183</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44459</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44123</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>44551</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44544</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44726</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44454</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>44358</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44496</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44760</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44513</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44558</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44484</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>44484</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44749</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>44277</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>44837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>44809</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44102</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>44123</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>44429</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44875</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44433</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44469</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44182</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44509</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>44531</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44277</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44673</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>44095</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>44282</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>44439</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>44120</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>44545</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44537</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>44182</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44182</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44704</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>44846</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45378</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44826</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>44820</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45135</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45600</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45363</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45079</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45455</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45373</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>44901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44120</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45779</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45281</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45393</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44091</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>44909</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45378</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44158</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44908</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45783.45171296296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45280</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>44880</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45786.49009259259</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>44896</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45786</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44903</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45021</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45560.34564814815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45469</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>45281</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>44412</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45786.53510416667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45408</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45040</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44910</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>45586</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45442</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45320</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45014</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45790.61496527777</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45789</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45226</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44909</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44909</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45140</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>44496</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45145</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>45454</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45245</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>44581</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45035</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44910</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45796</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44440</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45428</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45457</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45560.34431712963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45576</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45453</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45561</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45798</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>45393</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45798</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>44851</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>44943</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45604</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45307</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>45618</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44550</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45415</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44637</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44911</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44915</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45805</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45805</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45545</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44566</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45621.595</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45147</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45316</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>45603</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45601</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>45223</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45663</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44924</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45093</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45279</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45611.49162037037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45713.54880787037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45313</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>44698</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45716</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45182</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45815</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45488</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>45041</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>44571</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45320</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45691</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45544</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>44789</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39395,7 +39395,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45247</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45819</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>45117</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45820</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45117</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44383</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>44952</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45663</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45107</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45226</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45740</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41624,7 +41624,7 @@
         <v>45371</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45687</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>44735</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45772</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45142</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45205</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>45261</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>44641</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45006.49</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>44719</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45226</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45251</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>44981</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>44735</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>45281</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>45124</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45694</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>44491</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>44830</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45135</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>44900</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>44933</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45881.63590277778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45881.6677199074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45881.67791666667</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>45239</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>44994</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44952</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45880</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>45881.40667824074</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45713</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>44887</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45279</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49367,7 +49367,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>44761</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45530</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45530</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45883.49055555555</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45883.51207175926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>45882.30746527778</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45078</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45239</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>44522</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45888.60806712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45887.43675925926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50924,7 +50924,7 @@
         <v>45457</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45457</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45888.31405092592</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45887.6322337963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51472,7 +51472,7 @@
         <v>45887.42543981481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45888.63608796296</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>44900</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45887.62902777778</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45888.59356481482</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45888.59829861111</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45142</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>45616</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45887.67797453704</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45890.35861111111</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45889.67865740741</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45890</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>45890</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         <v>45890.45545138889</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45889.52583333333</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>45890.61520833334</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53783,7 +53783,7 @@
         <v>45889.82722222222</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>45672</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53959,7 +53959,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -54021,7 +54021,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>45713.36498842593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>45890.42685185185</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>45889.33643518519</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>45890.46518518519</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>45890.47592592592</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -54393,7 +54393,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45889.34109953704</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45889.67777777778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>45889.67834490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45890.43667824074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>45271</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54760,7 +54760,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54884,7 +54884,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45849</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>44733</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>45894</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45681</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -55355,7 +55355,7 @@
         <v>45849</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45894.4565162037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>45891</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>45271</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55774,7 +55774,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55836,7 +55836,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55960,7 +55960,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -56265,7 +56265,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -56327,7 +56327,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45895.46971064815</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>44620</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56694,7 +56694,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>44735</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45701</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45896.60385416666</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45705</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>44894</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45896.63950231481</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57542,7 +57542,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>45149</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>44861</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45468</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57842,7 +57842,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57899,7 +57899,7 @@
         <v>45897.38390046296</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>45897.37753472223</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>45740</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>44875</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -58385,7 +58385,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58504,7 +58504,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58566,7 +58566,7 @@
         <v>45813</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>45898.37825231482</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>45898.43600694444</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -59052,7 +59052,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>44847</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -59233,7 +59233,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -59295,7 +59295,7 @@
         <v>45187</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         <v>44812</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59652,7 +59652,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59709,7 +59709,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>44501</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45666</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59890,7 +59890,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -60014,7 +60014,7 @@
         <v>44830</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         <v>44403</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -60128,7 +60128,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -60185,7 +60185,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -60242,7 +60242,7 @@
         <v>44820</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>44907</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>44603</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
         <v>44424</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         <v>44826</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60537,7 +60537,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60594,7 +60594,7 @@
         <v>45176</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60651,7 +60651,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>45279</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>44874</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60827,7 +60827,7 @@
         <v>44874</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60889,7 +60889,7 @@
         <v>45775</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>44890</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>44670</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -61360,7 +61360,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61422,7 +61422,7 @@
         <v>45561</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>45107</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61541,7 +61541,7 @@
         <v>45107</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61660,7 +61660,7 @@
         <v>45266</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>44083</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>44323</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>44826</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>44369</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>44580</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -62131,7 +62131,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -62188,7 +62188,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45709</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -62302,7 +62302,7 @@
         <v>44620</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>44881</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>44642</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>44963</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62768,7 +62768,7 @@
         <v>45098</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62825,7 +62825,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62944,7 +62944,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -63006,7 +63006,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>45015</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -63239,7 +63239,7 @@
         <v>45091</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>44823</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63363,7 +63363,7 @@
         <v>45223</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63420,7 +63420,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45103</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45058</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>44876</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>44477</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>45020</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45701</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>44466</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -64119,7 +64119,7 @@
         <v>45406</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -64176,7 +64176,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -64238,7 +64238,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64295,7 +64295,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45732</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64595,7 +64595,7 @@
         <v>45555</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64652,7 +64652,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64714,7 +64714,7 @@
         <v>44903</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64838,7 +64838,7 @@
         <v>44952</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64957,7 +64957,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -65019,7 +65019,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -65081,7 +65081,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -65262,7 +65262,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65324,7 +65324,7 @@
         <v>44886</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65443,7 +65443,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65505,7 +65505,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>44603</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>45271</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65681,7 +65681,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>45101</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65862,7 +65862,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65924,7 +65924,7 @@
         <v>45097</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65986,7 +65986,7 @@
         <v>45238</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -66043,7 +66043,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -66105,7 +66105,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -66167,7 +66167,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -66229,7 +66229,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -66286,7 +66286,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>45041</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45462</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66524,7 +66524,7 @@
         <v>45156</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45599</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66648,7 +66648,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66710,7 +66710,7 @@
         <v>45541</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66772,7 +66772,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66834,7 +66834,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -67010,7 +67010,7 @@
         <v>45176</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -67067,7 +67067,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -67129,7 +67129,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -67191,7 +67191,7 @@
         <v>44529</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -67248,7 +67248,7 @@
         <v>45503</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -67305,7 +67305,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67367,7 +67367,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67429,7 +67429,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67491,7 +67491,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67553,7 +67553,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67615,7 +67615,7 @@
         <v>45091</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67677,7 +67677,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67739,7 +67739,7 @@
         <v>44924</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67796,7 +67796,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67858,7 +67858,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67915,7 +67915,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -67977,7 +67977,7 @@
         <v>45328</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -68034,7 +68034,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -68096,7 +68096,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -68158,7 +68158,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -68220,7 +68220,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -68282,7 +68282,7 @@
         <v>45063</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -68339,7 +68339,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68401,7 +68401,7 @@
         <v>45751</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68463,7 +68463,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68525,7 +68525,7 @@
         <v>45594</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68587,7 +68587,7 @@
         <v>45593</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68649,7 +68649,7 @@
         <v>45155</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68711,7 +68711,7 @@
         <v>45635</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68768,7 +68768,7 @@
         <v>45308</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68830,7 +68830,7 @@
         <v>45583</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68887,7 +68887,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -68949,7 +68949,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -69011,7 +69011,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -69073,7 +69073,7 @@
         <v>45211</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -69135,7 +69135,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -69197,7 +69197,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -69259,7 +69259,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -69321,7 +69321,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69378,7 +69378,7 @@
         <v>45101</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69435,7 +69435,7 @@
         <v>45233</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69492,7 +69492,7 @@
         <v>45219</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69554,7 +69554,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69616,7 +69616,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -69673,7 +69673,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -69735,7 +69735,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -69797,7 +69797,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -69911,7 +69911,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -69973,7 +69973,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -70030,7 +70030,7 @@
         <v>45615</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -70092,7 +70092,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -70149,7 +70149,7 @@
         <v>44980</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -70206,7 +70206,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -70268,7 +70268,7 @@
         <v>45595</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -70330,7 +70330,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -70387,7 +70387,7 @@
         <v>45364</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -70444,7 +70444,7 @@
         <v>45588</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -70501,7 +70501,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -70558,7 +70558,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -70620,7 +70620,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -70682,7 +70682,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -70744,7 +70744,7 @@
         <v>45174</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -70806,7 +70806,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -70863,7 +70863,7 @@
         <v>45155</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -70925,7 +70925,7 @@
         <v>45279</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -70982,7 +70982,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -71044,7 +71044,7 @@
         <v>45373</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -71101,7 +71101,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -71163,7 +71163,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -71225,7 +71225,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -71282,7 +71282,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -71339,7 +71339,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -71396,7 +71396,7 @@
         <v>44909</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -71458,7 +71458,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C1103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -71520,7 +71520,7 @@
         <v>45546</v>
       </c>
       <c r="C1104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -71577,7 +71577,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C1105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -71639,7 +71639,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C1106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -71701,7 +71701,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C1107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45887.46398148148</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>45488</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>44433</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45877.46135416667</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>44902</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45217</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45798</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>45161</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44103</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45672</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45152</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>44820</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44132</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>44412</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45624</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44980</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44749</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44433</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45589</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45890.44530092592</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44501</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45618</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45231</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>45590</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45300</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>45887.62298611111</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44601</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44501</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45363</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44902</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>45877.56935185185</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45887.42761574074</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>45411</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45016</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45103</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44615</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44494</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44616</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44795</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44795</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45299</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45665.42216435185</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45786.47950231482</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45579</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45791.61121527778</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45533.4471875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45798</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45461.35597222222</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45595</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45653.36229166666</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45622</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45231</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45637.64248842592</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45818.61664351852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45594</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45820.55273148148</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>45831.51394675926</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45831.45858796296</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45831.54038194445</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45833.32979166666</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45881.41111111111</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45889.29927083333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45889.40121527778</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45849.61287037037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45853.61649305555</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45853.59981481481</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45853.58109953703</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45863.44873842593</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45251</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45694.35394675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45541.57616898148</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44543</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>44897</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45520.43246527778</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45580.65900462963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>45478.68777777778</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45552.36100694445</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45602</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45162.50637731481</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45470</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45561.34743055556</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>44376</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>44081</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44147</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44386</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>44495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44403</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44805.5905324074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44567.84981481481</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44426</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44095</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>44484.65474537037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>44585</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>44120</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44446.59321759259</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44469</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44388.59247685185</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>44403</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44535.39266203704</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44785.94342592593</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44874</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44354</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44783.5321875</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44448.48563657407</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44802.7690625</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44711</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44475</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44496.42803240741</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44784</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44120</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44622.92310185185</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44376.69396990741</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44109</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>44407</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44405</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44105</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44749.66362268518</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44490</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44501.35502314815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44839</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44777</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44761</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44882.3720949074</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>44805</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44564</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44439</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44388.58075231482</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44742</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44711</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44348.93670138889</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>44805</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44502.33094907407</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44502.34732638889</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>44501.4425462963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44515</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44109</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>44501.53170138889</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>44201</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>44473.94274305556</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44183</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>44783.53452546296</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>44459</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>44481</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>44123</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44551</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44867.43387731481</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44496</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44358</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44760</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44513</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44558</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44731.46202546296</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44484</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44749</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44484</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44809</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>44837</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>44429</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44433</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44469</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44123</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44277</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44875</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44102</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44182</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44531</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44446.6496412037</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44282</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>44282.3640625</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>44095</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>44120</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44439</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>44509</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>44501.41797453703</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44277</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44673</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>44437.3965625</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>44798.92728009259</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>44564.92136574074</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>44537</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>44545</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44182</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44182</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44356.93547453704</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44083</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45608.51774305556</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>44383</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44846</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44826</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45698.34989583334</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44704</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44726</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45454.38533564815</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45561</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44454</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45520.52563657407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>44670</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45455.9684837963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44846</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44532.41537037037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>44963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45211</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45546</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44544</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45541.38083333334</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45196.60607638889</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45251</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45618</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45775</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45672</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45534.57965277778</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45505.9484837963</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44158</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45629.36464120371</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45629.36469907407</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45035</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45457</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>44894</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45751.33399305555</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45665.64759259259</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45645.59473379629</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45408</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45701</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44880</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45468</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>45625.63980324074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45705.49078703704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45777.44641203704</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45776.45245370371</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45777.55637731482</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45777.46550925926</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45328</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45558.62386574074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45558.62707175926</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45779.42604166667</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44876</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45779.46914351852</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44120</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45779.61503472222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45779</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>45782.44893518519</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45617.73600694445</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>45715.55240740741</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>44924.94077546296</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45520.53516203703</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45520.53523148148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45783.57331018519</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45762.51096064815</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45135</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45576.64849537037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44915.44746527778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44120.54900462963</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44909</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>45320</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45784.43131944445</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44861</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45561.62664351852</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45561.63295138889</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44901</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45785.66422453704</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45785.49008101852</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45785.53003472222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45142</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45107</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45107</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45742.41636574074</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44845.48649305556</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45488.41469907408</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45784.36506944444</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45457.60049768518</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45415</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45681</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>44761</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>44901</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>44412</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45574.5038425926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44323</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45544.55925925926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44915</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45232.60467592593</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45742.87837962963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45561.63130787037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44369</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45758.39929398148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45479.94907407407</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45479.94927083333</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45789.61988425926</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45786</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>45786.60216435185</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45513.31015046296</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>45617.26189814815</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45789</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45786.36578703704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45786.44856481482</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45429.37934027778</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45789.58261574074</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45611.40226851852</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45576.4328587963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45313</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45280</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45611.58083333333</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45613.77569444444</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45182</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45474.61927083333</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45320</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45586.57693287037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45786.44841435185</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45751</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45624.46928240741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>45789.5709375</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45279</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>45432.70289351852</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45786.60395833333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45786.6059837963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45103.49182870371</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44874</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45616</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44904.64789351852</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45475.60128472222</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44942.36244212963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44477</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44830</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45786.5633912037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45561.35800925926</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44642</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45635.61909722222</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45635.65770833333</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45595</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>44851</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45238</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45770.59820601852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45545</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45378.71258101852</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45793.59476851852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45555.64177083333</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45793.55598379629</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45792.57557870371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45793.55439814815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44571.42083333333</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45740.64665509259</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44896</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45793.55248842593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45503</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45615.65667824074</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45792.57373842593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>44735</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>45271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45561.58484953704</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45559.5952662037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>45462.81574074074</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>45646.38721064815</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45646.40891203703</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45140</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45793.32454861111</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44876.63155092593</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45792.69283564815</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>45154.64055555555</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>45796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45149</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>44518.92194444445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45756.39481481481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>45457</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45457.57278935185</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44453.44574074074</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45225.96839120371</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44440</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45457</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44910</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44952</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45715.59436342592</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45453</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45014</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45540.59409722222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45513.58017361111</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45226.96270833333</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45509.67273148148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45365.3941550926</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44581</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45600</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>45534.6363425926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45629.56875</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45629.55165509259</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45750.57883101852</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45279</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45694</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45147.95506944445</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>44925.63133101852</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45796.53043981481</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45775.65394675926</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45561.3359375</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45041</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45798</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>45106.62175925926</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>44924</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45606.8803587963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45516.56430555556</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44512.6299537037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45798.40518518518</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45798.40986111111</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45266</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45799.39927083333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45799.69825231482</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>45187.64328703703</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45198.93778935185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45799.56951388889</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>44812</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45799.34076388889</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45103.50481481481</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45798.41498842592</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45106.64143518519</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>44903.92716435185</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45799.61918981482</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45798.57329861111</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33832,7 +33832,7 @@
         <v>45236.63934027778</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45677.48184027777</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45799.5315162037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45677.56866898148</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45798</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>44468.56100694444</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45798.40288194444</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45541</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45576.64476851852</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45803.57362268519</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45687</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45392.57258101852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45803.56601851852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45769.48415509259</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45803.49502314815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>45744.61188657407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45803.41887731481</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45406.96375</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45803.45731481481</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>45803.4812962963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>45646.42950231482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45761.38211805555</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>45247.67944444445</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45063</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45803.47020833333</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45555</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45555.55739583333</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45803.61508101852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44820</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45218.63373842592</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45078</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44912.69100694444</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>44994.59267361111</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>45805.50157407407</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45552.38758101852</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>44733</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45428</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45491.66295138889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45526.69534722222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45468.97400462963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45805.63583333333</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>44886</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45805.43233796296</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45805.56206018518</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45208.3863425926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45469</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45546.73186342593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45124</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>44913.44049768519</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45629.35606481481</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45805</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>45805</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>45568.43364583333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>45652.73207175926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45807.37386574074</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>44907</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45281</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45807.34731481481</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45807.36931712963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45807.31575231482</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45350.95329861111</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>44540.38878472222</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>45811.64100694445</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45621.595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45442</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45135</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>45810.32515046297</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45308</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45811.44082175926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45811.65400462963</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>45174</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>45520.53105324074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>44973.39023148148</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45811.33413194444</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>44566</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>44469.38017361111</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>45040</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45474.95578703703</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45544</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>45544.51636574074</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45469.55527777778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45223</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44911</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45316</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45279</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45685.49891203704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45461.9625</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45763.59829861111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45763.63334490741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45813.50950231482</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45588</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45813.36581018518</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45813.48702546296</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45813.52065972222</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45813.57643518518</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45813.59416666667</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45566.73494212963</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>45364</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39755,7 +39755,7 @@
         <v>45586</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45576.48979166667</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45813.48407407408</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45813.53611111111</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45637.49741898148</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>45770.46910879629</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45812.57329861111</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45155</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45006.48116898148</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45247</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45691</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
         <v>45815.323125</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>44501</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>44910</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>45554.4563425926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45815</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45474.4971875</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45223</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45708.61552083334</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45818.61637731481</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45818.69081018519</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45117</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45239</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45105.70230324074</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45515.85923611111</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>45154</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>45819</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45818.37524305555</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45488</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45821.54648148148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45820.55636574074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>44924</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45821.56167824074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45821.44274305556</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45579.5771875</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44980</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45821.59451388889</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45821.45783564815</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45820</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45820.54582175926</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45820.54883101852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45621.6587037037</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45825.65462962963</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45866.61493055556</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45223</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45824.65788194445</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45161.58166666667</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45822.96603009259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45371.55444444445</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>44403</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>45824.34488425926</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45825.56317129629</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>45868.63600694444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45826.68275462963</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45281</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45827.42743055556</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45827.61538194444</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>45827.51121527778</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45827.5730787037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45827.31850694444</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45826.35212962963</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>45831.4724074074</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45831.50633101852</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45873.41922453704</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>45831.47189814815</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45831.41046296297</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45873.46443287037</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45873.52534722222</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45873.44997685185</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45831.62481481482</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>45831.41945601852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45831.42626157407</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45594</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45831.4783912037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45832.3215162037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45832.36453703704</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45875.42446759259</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>44735</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>45832.55611111111</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45832.35980324074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45832.57369212963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45261</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45832.31803240741</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45637.55984953704</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45832.55402777778</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45832.51869212963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45307</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45834.55274305555</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45834.35741898148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45834.40671296296</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45621.43199074074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45835.59662037037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45618.40399305556</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45834.67758101852</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45835.34858796297</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45151.94417824074</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45835.47898148148</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45441.85773148148</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45835.61503472222</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45378</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>45835.34505787037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>45834.3474537037</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -46013,7 +46013,7 @@
         <v>45839.42896990741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45470.40854166666</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45838.64458333333</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>44981</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45869.6568287037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45503.65972222222</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45869.38572916666</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45839.67783564814</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>45838.40033564815</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45838.64195601852</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45880</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45881.63590277778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>45881.6677199074</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>45839.38622685185</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>45875.47822916666</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>45838.33060185185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>45838.44355324074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>45873.42712962963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45873.6340162037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>45881.40667824074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>45838.36606481481</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>45839.47989583333</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45881.67791666667</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>45841.54920138889</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>45841.46954861111</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>45841.4374537037</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45841.40428240741</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45841.48503472222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>45840.42515046296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>45840.44748842593</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45841.44836805556</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45841.44326388889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45843.60467592593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>45845.33821759259</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45845.50052083333</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45887.42543981481</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45887.67797453704</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>45887.6322337963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45887.43675925926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>45128.64351851852</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>45520.53451388889</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>44887</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>45883.49055555555</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45883.51207175926</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45887.62902777778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45147</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>45842.75030092592</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45843.61037037037</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45845.49877314815</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -49038,7 +49038,7 @@
         <v>45882.30746527778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>44344.93608796296</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>45847.34548611111</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45590.58260416667</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45888.60806712963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>45847.43788194445</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45889.67865740741</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45888.31405092592</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>45889.67777777778</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45889.67834490741</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45889.82722222222</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>45889.33643518519</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>44641</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45889.34109953704</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45888.59356481482</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45888.63608796296</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>45888.59829861111</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45889.52583333333</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45107</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45849.51625</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45849.55733796296</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -50330,7 +50330,7 @@
         <v>45462</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -50387,7 +50387,7 @@
         <v>45520.52138888889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45849.54935185185</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -50511,7 +50511,7 @@
         <v>45849.58274305556</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45849.62559027778</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>45890</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -50692,7 +50692,7 @@
         <v>45890</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45890.45545138889</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>44826</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>44902.54416666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45141.96019675926</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45849.60525462963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45890.46518518519</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>45849</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>45849.54143518519</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>45890.42685185185</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45890.47592592592</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>45890.43667824074</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45890.35861111111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45849.49472222223</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45891</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>45849.60534722222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45849</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45849.59119212963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>45849.55927083334</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45890.61520833334</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -51907,7 +51907,7 @@
         <v>45853.62052083333</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>45894</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -52026,7 +52026,7 @@
         <v>45853.35604166667</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>45853.61248842593</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>45895.46971064815</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>45852.63579861111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45853.57862268519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>45853.58521990741</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -52398,7 +52398,7 @@
         <v>45853.6025</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>45373</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -52517,7 +52517,7 @@
         <v>45853.59733796296</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45853.60569444444</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -52641,7 +52641,7 @@
         <v>45545.52331018518</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45894.4565162037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>45231.43283564815</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45854.57362268519</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>45897.37753472223</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45896.63950231481</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>45854.57376157407</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>45896.60385416666</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45897.38390046296</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>45813</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>45854.42938657408</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -53303,7 +53303,7 @@
         <v>45705</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>45041</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>44672.92575231481</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -53479,7 +53479,7 @@
         <v>45859.32412037037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -53536,7 +53536,7 @@
         <v>44840.30355324074</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>45701</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>45898.37825231482</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45856.55252314815</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>45859.61498842593</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -53898,7 +53898,7 @@
         <v>45901.66380787037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45898.43600694444</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -54017,7 +54017,7 @@
         <v>44900</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>45188.9247800926</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>44904.60694444444</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45859.62431712963</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45861.51261574074</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45861.57894675926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -54379,7 +54379,7 @@
         <v>45903.64262731482</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -54436,7 +54436,7 @@
         <v>45861.50935185186</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45903.63274305555</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45205</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45861.55245370371</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45903.59854166667</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45861.63883101852</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45700.63939814815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -54860,7 +54860,7 @@
         <v>45859.32984953704</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         <v>45903.40899305556</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54979,7 +54979,7 @@
         <v>45492.96038194445</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -55041,7 +55041,7 @@
         <v>45903.40400462963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>45903.58563657408</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45245</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45652.71194444445</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>45226</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>45226</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>44826</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>45614.42590277778</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -55522,7 +55522,7 @@
         <v>45737.6024537037</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>45460.95396990741</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>45904.41127314815</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45905.71912037037</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45863.47090277778</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>45905.37756944444</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>45862.56438657407</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -55951,7 +55951,7 @@
         <v>45905.52245370371</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -56013,7 +56013,7 @@
         <v>44908</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -56070,7 +56070,7 @@
         <v>44735</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>45233</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -56184,7 +56184,7 @@
         <v>44900</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>44875</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>45545.38578703703</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>44491</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>44890</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45443.61378472222</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45520.52381944445</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -56613,7 +56613,7 @@
         <v>45103</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>44994.94163194444</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45715.59438657408</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -56794,7 +56794,7 @@
         <v>45101</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -56851,7 +56851,7 @@
         <v>44952</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>45705.72366898148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>45210.55800925926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>44943</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -57084,7 +57084,7 @@
         <v>45520.51114583333</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45520.52251157408</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>44830</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45356.42712962963</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>45632.65679398148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -57384,7 +57384,7 @@
         <v>45599</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>44522</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -57508,7 +57508,7 @@
         <v>45491.67836805555</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -57570,7 +57570,7 @@
         <v>45730.46041666667</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>45058</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -57684,7 +57684,7 @@
         <v>44468.55635416666</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -57741,7 +57741,7 @@
         <v>45741.32619212963</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -57798,7 +57798,7 @@
         <v>45441.85204861111</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -57855,7 +57855,7 @@
         <v>45613.74923611111</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -57917,7 +57917,7 @@
         <v>45149.59932870371</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57974,7 +57974,7 @@
         <v>45145</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -58036,7 +58036,7 @@
         <v>45352.58462962963</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -58098,7 +58098,7 @@
         <v>45226.96280092592</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45142</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>44750.54626157408</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -58284,7 +58284,7 @@
         <v>45176.39111111111</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -58346,7 +58346,7 @@
         <v>45573.51078703703</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45531.6409375</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         <v>45590.62112268519</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>45393</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>44830.44271990741</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>44909</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45574.53748842593</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -58780,7 +58780,7 @@
         <v>45555.37684027778</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>45673.67935185185</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -58894,7 +58894,7 @@
         <v>45621.62319444444</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -58951,7 +58951,7 @@
         <v>45506.61575231481</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -59013,7 +59013,7 @@
         <v>45117</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -59075,7 +59075,7 @@
         <v>45764.360625</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -59137,7 +59137,7 @@
         <v>45673.62765046296</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -59194,7 +59194,7 @@
         <v>45596.64743055555</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -59256,7 +59256,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -59313,7 +59313,7 @@
         <v>44924.71886574074</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -59375,7 +59375,7 @@
         <v>45477.54815972222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>45534.63637731481</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>45560.48015046296</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -59556,7 +59556,7 @@
         <v>45093</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -59618,7 +59618,7 @@
         <v>44540.39224537037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -59675,7 +59675,7 @@
         <v>45559.44234953704</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -59737,7 +59737,7 @@
         <v>44466</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -59794,7 +59794,7 @@
         <v>44637</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>44484.64653935185</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>45527.32915509259</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>45775.37510416667</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -60032,7 +60032,7 @@
         <v>45743.68226851852</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -60089,7 +60089,7 @@
         <v>45534.36832175926</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>45281</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>45226</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -60265,7 +60265,7 @@
         <v>45608.61015046296</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -60327,7 +60327,7 @@
         <v>45271</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -60384,7 +60384,7 @@
         <v>45201.64815972222</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -60441,7 +60441,7 @@
         <v>44534.49537037037</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -60498,7 +60498,7 @@
         <v>45555.60515046296</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>44486.67993055555</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -60617,7 +60617,7 @@
         <v>44933</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -60674,7 +60674,7 @@
         <v>45713.59445601852</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -60736,7 +60736,7 @@
         <v>45713.59461805555</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -60798,7 +60798,7 @@
         <v>44973.46649305556</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -60855,7 +60855,7 @@
         <v>45565.69086805556</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>45079.92747685185</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60969,7 +60969,7 @@
         <v>45479.949375</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -61031,7 +61031,7 @@
         <v>45006.49</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -61088,7 +61088,7 @@
         <v>44496</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -61150,7 +61150,7 @@
         <v>45454</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -61207,7 +61207,7 @@
         <v>45772.56854166667</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45643.63650462963</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>44789</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>45611.53107638889</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -61455,7 +61455,7 @@
         <v>45621.55994212963</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -61517,7 +61517,7 @@
         <v>45617.49065972222</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45603</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>45258.38234953704</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -61698,7 +61698,7 @@
         <v>45279</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -61755,7 +61755,7 @@
         <v>45411.60519675926</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45156</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>45490.69914351852</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>45652.74261574074</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>45373</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45520.51587962963</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -62112,7 +62112,7 @@
         <v>44823</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>44934.85548611111</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45751.32021990741</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -62298,7 +62298,7 @@
         <v>45695.34431712963</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -62360,7 +62360,7 @@
         <v>44620</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>45713</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -62474,7 +62474,7 @@
         <v>45713.44863425926</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -62531,7 +62531,7 @@
         <v>45520.526875</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -62593,7 +62593,7 @@
         <v>45520.53230324074</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -62655,7 +62655,7 @@
         <v>45524.61850694445</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -62712,7 +62712,7 @@
         <v>45740</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>45363</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>44881</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -62893,7 +62893,7 @@
         <v>44994</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62950,7 +62950,7 @@
         <v>45483.93377314815</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>45635.44981481481</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -63069,7 +63069,7 @@
         <v>45732</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -63126,7 +63126,7 @@
         <v>44424</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>45101</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>45740</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -63307,7 +63307,7 @@
         <v>45772.34459490741</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -63364,7 +63364,7 @@
         <v>45772.36483796296</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -63421,7 +63421,7 @@
         <v>45527.36991898148</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -63483,7 +63483,7 @@
         <v>45688.67435185185</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -63545,7 +63545,7 @@
         <v>44620</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -63602,7 +63602,7 @@
         <v>44456.50484953704</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         <v>45723.57395833333</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -63726,7 +63726,7 @@
         <v>45763.48305555555</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>45079</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>45601</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63902,7 +63902,7 @@
         <v>44903</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63964,7 +63964,7 @@
         <v>44580</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -64021,7 +64021,7 @@
         <v>45635</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -64078,7 +64078,7 @@
         <v>44909</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -64140,7 +64140,7 @@
         <v>45530</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -64202,7 +64202,7 @@
         <v>45530</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -64259,7 +64259,7 @@
         <v>45700.54133101852</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -64316,7 +64316,7 @@
         <v>45406</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -64373,7 +64373,7 @@
         <v>45593</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -64435,7 +64435,7 @@
         <v>44572.68023148148</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -64492,7 +64492,7 @@
         <v>45512.68542824074</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -64554,7 +64554,7 @@
         <v>44910.49471064815</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -64616,7 +64616,7 @@
         <v>45744.58421296296</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -64678,7 +64678,7 @@
         <v>45021</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -64735,7 +64735,7 @@
         <v>45666</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -64792,7 +64792,7 @@
         <v>45551.41628472223</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -64849,7 +64849,7 @@
         <v>45638.64100694445</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45496.53711805555</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45590.52324074074</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45576.45649305556</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>44847</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -65154,7 +65154,7 @@
         <v>45608.46447916667</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -65216,7 +65216,7 @@
         <v>44534.51119212963</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>45615</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -65335,7 +65335,7 @@
         <v>45534.64569444444</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -65397,7 +65397,7 @@
         <v>45145.64986111111</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -65459,7 +65459,7 @@
         <v>44459.92047453704</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>45700.67916666667</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45716</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45646.3871412037</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>44909</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>44603</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -65806,7 +65806,7 @@
         <v>45176</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -65863,7 +65863,7 @@
         <v>45713.46909722222</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65920,7 +65920,7 @@
         <v>45709.73266203704</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65977,7 +65977,7 @@
         <v>44448.47038194445</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -66034,7 +66034,7 @@
         <v>45709</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -66091,7 +66091,7 @@
         <v>45526.47052083333</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>45077.94409722222</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -66215,7 +66215,7 @@
         <v>45618.3540162037</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>44979.3956712963</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -66334,7 +66334,7 @@
         <v>44903</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -66396,7 +66396,7 @@
         <v>45097</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -66458,7 +66458,7 @@
         <v>45114.58961805556</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -66520,7 +66520,7 @@
         <v>45048.92655092593</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -66577,7 +66577,7 @@
         <v>45758.46924768519</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -66639,7 +66639,7 @@
         <v>45541.56019675926</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -66701,7 +66701,7 @@
         <v>45155</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -66763,7 +66763,7 @@
         <v>45763.61390046297</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -66820,7 +66820,7 @@
         <v>45098</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -66877,7 +66877,7 @@
         <v>45075</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66939,7 +66939,7 @@
         <v>45075</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -67001,7 +67001,7 @@
         <v>45495.56212962963</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -67063,7 +67063,7 @@
         <v>45593.719375</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -67125,7 +67125,7 @@
         <v>45219</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -67187,7 +67187,7 @@
         <v>45516.63974537037</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -67244,7 +67244,7 @@
         <v>45721.5528587963</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -67306,7 +67306,7 @@
         <v>45616.8405324074</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -67368,7 +67368,7 @@
         <v>44874</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -67430,7 +67430,7 @@
         <v>45615.57329861111</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -67492,7 +67492,7 @@
         <v>45615.5746412037</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -67554,7 +67554,7 @@
         <v>45615.57478009259</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -67616,7 +67616,7 @@
         <v>45638.34984953704</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -67673,7 +67673,7 @@
         <v>45590.58554398148</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>45455</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -67797,7 +67797,7 @@
         <v>45772</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -67854,7 +67854,7 @@
         <v>45475.94980324074</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -67916,7 +67916,7 @@
         <v>45475.95016203704</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67978,7 +67978,7 @@
         <v>44952</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -68035,7 +68035,7 @@
         <v>45271</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -68092,7 +68092,7 @@
         <v>45513.33157407407</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -68154,7 +68154,7 @@
         <v>45240.28634259259</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -68211,7 +68211,7 @@
         <v>45541.36966435185</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -68273,7 +68273,7 @@
         <v>45209.64944444445</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -68330,7 +68330,7 @@
         <v>44091</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -68387,7 +68387,7 @@
         <v>45103</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -68449,7 +68449,7 @@
         <v>44820</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -68506,7 +68506,7 @@
         <v>45576</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -68568,7 +68568,7 @@
         <v>45604</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -68625,7 +68625,7 @@
         <v>44719</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -68682,7 +68682,7 @@
         <v>45630.34428240741</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -68744,7 +68744,7 @@
         <v>45643.79216435185</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -68801,7 +68801,7 @@
         <v>45616.83502314815</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -68863,7 +68863,7 @@
         <v>45176</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -68920,7 +68920,7 @@
         <v>45020</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68977,7 +68977,7 @@
         <v>44603</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -69034,7 +69034,7 @@
         <v>45583</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -69091,7 +69091,7 @@
         <v>45533.48732638889</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -69153,7 +69153,7 @@
         <v>45572.45052083334</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -69210,7 +69210,7 @@
         <v>44698</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -69272,7 +69272,7 @@
         <v>45187</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -69334,7 +69334,7 @@
         <v>45015</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -69391,7 +69391,7 @@
         <v>45569.40431712963</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -69453,7 +69453,7 @@
         <v>45576.48423611111</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -69515,7 +69515,7 @@
         <v>45576.58394675926</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -69577,7 +69577,7 @@
         <v>45573.68590277778</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -69634,7 +69634,7 @@
         <v>45091</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -69696,7 +69696,7 @@
         <v>45468.36027777778</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -69753,7 +69753,7 @@
         <v>45713.67753472222</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>45265.95865740741</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -69877,7 +69877,7 @@
         <v>45600.36332175926</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -69934,7 +69934,7 @@
         <v>45561</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -69996,7 +69996,7 @@
         <v>44904.59792824074</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -70058,7 +70058,7 @@
         <v>45478.6802662037</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -70120,7 +70120,7 @@
         <v>45742.69009259259</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -70182,7 +70182,7 @@
         <v>45742.87457175926</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -70239,7 +70239,7 @@
         <v>44529</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -70296,7 +70296,7 @@
         <v>45103</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -70358,7 +70358,7 @@
         <v>45103.50075231482</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -70420,7 +70420,7 @@
         <v>45163.92709490741</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -70477,7 +70477,7 @@
         <v>45357.47782407407</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -70534,7 +70534,7 @@
         <v>45154.53600694444</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -70591,7 +70591,7 @@
         <v>45730.45533564815</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -70648,7 +70648,7 @@
         <v>44550</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -70705,7 +70705,7 @@
         <v>44973.48649305556</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -70762,7 +70762,7 @@
         <v>45378</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -70819,7 +70819,7 @@
         <v>45763.45278935185</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -70881,7 +70881,7 @@
         <v>45173.4409375</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -70943,7 +70943,7 @@
         <v>45457.61990740741</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -71005,7 +71005,7 @@
         <v>45586.52850694444</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -71067,7 +71067,7 @@
         <v>45498.47368055556</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -71124,7 +71124,7 @@
         <v>45061.94275462963</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -71186,7 +71186,7 @@
         <v>45604.42814814814</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>

--- a/Översikt LYCKSELE.xlsx
+++ b/Översikt LYCKSELE.xlsx
@@ -567,7 +567,7 @@
         <v>45887.46398148148</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>45488</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>44433</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44357.45625</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45611.60192129629</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>44902</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>45877.46135416667</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45217</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45621.65283564815</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45798</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>45161</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>44103</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>45845.3308912037</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>44508.92318287037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45672</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45831.53586805556</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45152</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>44820</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45460.95407407408</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45839.43550925926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45520.35296296296</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44132</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>44412</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44609.3165162037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45791.60834490741</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45623.70361111111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45782.62307870371</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45624</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45853.48318287037</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44980</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44749</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44433</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45610.66724537037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45618.66777777778</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45811.63672453703</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45589</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45827.604375</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45611.53018518518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45890.44530092592</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45520.34674768519</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45623.47923611111</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44501</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45629.65383101852</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45786.47642361111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>45785.52142361111</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45618.50975694445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>45643.54054398148</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>45637.62774305556</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45300</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45611.5784375</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45694.39746527778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45841.36038194445</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>45887.62298611111</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45590</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45618</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45617.63777777777</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44601</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44533.92109953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44286.32886574074</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44501</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45736.6775</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45772.47297453704</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45103</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45786.46878472222</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>45770.38863425926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45786.46645833334</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45789.43789351852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>45580.5121412037</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>45791.65668981482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45791.63113425926</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45411</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>45793.66493055555</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45706.4094212963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>45805.59424768519</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>44902</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45559.55326388889</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45818.37267361111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45541.43171296296</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>44945.50438657407</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45831.51792824074</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45831.33053240741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45162.4615625</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45363</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45877.56935185185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>45608.6122337963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45887.42761574074</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45845.36605324074</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45904.41127314815</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45016</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>45912.34836805556</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44495.33185185185</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>44587.54111111111</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44615</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44494</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44616</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44795</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44795</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>45652.74872685185</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44551.40773148148</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45660.34533564815</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45777.4309375</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45777.42574074074</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45299</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v